--- a/光伏配储项目/电价数据/2026/赞化站.xlsx
+++ b/光伏配储项目/电价数据/2026/赞化站.xlsx
@@ -16,10 +16,9 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="3">
+  <numFmts count="2">
     <numFmt numFmtId="164" formatCode="yyyy-mm-dd h:mm:ss"/>
     <numFmt numFmtId="165" formatCode="YYYY-MM-DD HH:MM:SS"/>
-    <numFmt numFmtId="166" formatCode="yyyy/mm/dd"/>
   </numFmts>
   <fonts count="2">
     <font>
@@ -64,7 +63,7 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="166" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -430,13 +429,13 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:CS116"/>
+  <dimension ref="A1:CS143"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>日期</t>
+          <t>date</t>
         </is>
       </c>
       <c r="B1" s="1" t="inlineStr">
@@ -34613,6 +34612,7917 @@
       </c>
       <c r="CS116" t="n">
         <v>0.43577</v>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" s="2" t="n">
+        <v>46138</v>
+      </c>
+      <c r="B117" t="n">
+        <v>0.38452</v>
+      </c>
+      <c r="C117" t="n">
+        <v>0.7835700000000001</v>
+      </c>
+      <c r="D117" t="n">
+        <v>0.48374</v>
+      </c>
+      <c r="E117" t="n">
+        <v>0.50452</v>
+      </c>
+      <c r="F117" t="n">
+        <v>0.44136</v>
+      </c>
+      <c r="G117" t="n">
+        <v>0.44584</v>
+      </c>
+      <c r="H117" t="n">
+        <v>0.39815</v>
+      </c>
+      <c r="I117" t="n">
+        <v>0.40839</v>
+      </c>
+      <c r="J117" t="n">
+        <v>0.39282</v>
+      </c>
+      <c r="K117" t="n">
+        <v>0.38296</v>
+      </c>
+      <c r="L117" t="n">
+        <v>0.3842</v>
+      </c>
+      <c r="M117" t="n">
+        <v>0.37475</v>
+      </c>
+      <c r="N117" t="n">
+        <v>0.37118</v>
+      </c>
+      <c r="O117" t="n">
+        <v>0.3691</v>
+      </c>
+      <c r="P117" t="n">
+        <v>0.36001</v>
+      </c>
+      <c r="Q117" t="n">
+        <v>0.37008</v>
+      </c>
+      <c r="R117" t="n">
+        <v>0.38045</v>
+      </c>
+      <c r="S117" t="n">
+        <v>0.3772799999999999</v>
+      </c>
+      <c r="T117" t="n">
+        <v>0.34138</v>
+      </c>
+      <c r="U117" t="n">
+        <v>0.36409</v>
+      </c>
+      <c r="V117" t="n">
+        <v>0.36018</v>
+      </c>
+      <c r="W117" t="n">
+        <v>0.38601</v>
+      </c>
+      <c r="X117" t="n">
+        <v>0.36645</v>
+      </c>
+      <c r="Y117" t="n">
+        <v>0.38865</v>
+      </c>
+      <c r="Z117" t="n">
+        <v>0.38362</v>
+      </c>
+      <c r="AA117" t="n">
+        <v>0.39205</v>
+      </c>
+      <c r="AB117" t="n">
+        <v>0.38484</v>
+      </c>
+      <c r="AC117" t="n">
+        <v>0.40308</v>
+      </c>
+      <c r="AD117" t="n">
+        <v>0.42567</v>
+      </c>
+      <c r="AE117" t="n">
+        <v>0.30002</v>
+      </c>
+      <c r="AF117" t="n">
+        <v>0.36589</v>
+      </c>
+      <c r="AG117" t="n">
+        <v>0.30829</v>
+      </c>
+      <c r="AH117" t="n">
+        <v>0.31091</v>
+      </c>
+      <c r="AI117" t="n">
+        <v>0.32087</v>
+      </c>
+      <c r="AJ117" t="n">
+        <v>0.33467</v>
+      </c>
+      <c r="AK117" t="n">
+        <v>0.35243</v>
+      </c>
+      <c r="AL117" t="n">
+        <v>0.32238</v>
+      </c>
+      <c r="AM117" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AN117" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AO117" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AP117" t="n">
+        <v>0.24113</v>
+      </c>
+      <c r="AQ117" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AR117" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AS117" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AT117" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AU117" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AV117" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AW117" t="n">
+        <v>0.14217</v>
+      </c>
+      <c r="AX117" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AY117" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AZ117" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BA117" t="n">
+        <v>0.00272</v>
+      </c>
+      <c r="BB117" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BC117" t="n">
+        <v>0.08353000000000001</v>
+      </c>
+      <c r="BD117" t="n">
+        <v>0.08729000000000001</v>
+      </c>
+      <c r="BE117" t="n">
+        <v>0.07292</v>
+      </c>
+      <c r="BF117" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BG117" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BH117" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BI117" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BJ117" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BK117" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BL117" t="n">
+        <v>0.29264</v>
+      </c>
+      <c r="BM117" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BN117" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BO117" t="n">
+        <v>0.33736</v>
+      </c>
+      <c r="BP117" t="n">
+        <v>0.5115</v>
+      </c>
+      <c r="BQ117" t="n">
+        <v>0.5562</v>
+      </c>
+      <c r="BR117" t="n">
+        <v>0.74088</v>
+      </c>
+      <c r="BS117" t="n">
+        <v>1.14279</v>
+      </c>
+      <c r="BT117" t="n">
+        <v>0.39607</v>
+      </c>
+      <c r="BU117" t="n">
+        <v>1.35422</v>
+      </c>
+      <c r="BV117" t="n">
+        <v>0.43351</v>
+      </c>
+      <c r="BW117" t="n">
+        <v>0.44025</v>
+      </c>
+      <c r="BX117" t="n">
+        <v>0.66661</v>
+      </c>
+      <c r="BY117" t="n">
+        <v>0.8885299999999999</v>
+      </c>
+      <c r="BZ117" t="n">
+        <v>0.4982799999999999</v>
+      </c>
+      <c r="CA117" t="n">
+        <v>1.21399</v>
+      </c>
+      <c r="CB117" t="n">
+        <v>1.34587</v>
+      </c>
+      <c r="CC117" t="n">
+        <v>1.17945</v>
+      </c>
+      <c r="CD117" t="n">
+        <v>1.02788</v>
+      </c>
+      <c r="CE117" t="n">
+        <v>1.30758</v>
+      </c>
+      <c r="CF117" t="n">
+        <v>1.40845</v>
+      </c>
+      <c r="CG117" t="n">
+        <v>0.45355</v>
+      </c>
+      <c r="CH117" t="n">
+        <v>0.7044900000000001</v>
+      </c>
+      <c r="CI117" t="n">
+        <v>0.7559</v>
+      </c>
+      <c r="CJ117" t="n">
+        <v>1.11741</v>
+      </c>
+      <c r="CK117" t="n">
+        <v>0.95004</v>
+      </c>
+      <c r="CL117" t="n">
+        <v>0.90863</v>
+      </c>
+      <c r="CM117" t="n">
+        <v>0.8064600000000001</v>
+      </c>
+      <c r="CN117" t="n">
+        <v>0.7685599999999999</v>
+      </c>
+      <c r="CO117" t="n">
+        <v>0.51854</v>
+      </c>
+      <c r="CP117" t="n">
+        <v>0.4893</v>
+      </c>
+      <c r="CQ117" t="n">
+        <v>0.46928</v>
+      </c>
+      <c r="CR117" t="n">
+        <v>0.42052</v>
+      </c>
+      <c r="CS117" t="n">
+        <v>0.43077</v>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" s="2" t="n">
+        <v>46139</v>
+      </c>
+      <c r="B118" t="n">
+        <v>0.32886</v>
+      </c>
+      <c r="C118" t="n">
+        <v>0.7300800000000001</v>
+      </c>
+      <c r="D118" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="E118" t="n">
+        <v>0.9059700000000001</v>
+      </c>
+      <c r="F118" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="G118" t="n">
+        <v>0.96892</v>
+      </c>
+      <c r="H118" t="n">
+        <v>0.51181</v>
+      </c>
+      <c r="I118" t="n">
+        <v>0.53922</v>
+      </c>
+      <c r="J118" t="n">
+        <v>0.51901</v>
+      </c>
+      <c r="K118" t="n">
+        <v>0.51915</v>
+      </c>
+      <c r="L118" t="n">
+        <v>0.50054</v>
+      </c>
+      <c r="M118" t="n">
+        <v>0.40702</v>
+      </c>
+      <c r="N118" t="n">
+        <v>0.48119</v>
+      </c>
+      <c r="O118" t="n">
+        <v>0.38368</v>
+      </c>
+      <c r="P118" t="n">
+        <v>0.391</v>
+      </c>
+      <c r="Q118" t="n">
+        <v>0.49838</v>
+      </c>
+      <c r="R118" t="n">
+        <v>0.33856</v>
+      </c>
+      <c r="S118" t="n">
+        <v>0.39825</v>
+      </c>
+      <c r="T118" t="n">
+        <v>0.3841</v>
+      </c>
+      <c r="U118" t="n">
+        <v>0.38395</v>
+      </c>
+      <c r="V118" t="n">
+        <v>0.46654</v>
+      </c>
+      <c r="W118" t="n">
+        <v>0.42654</v>
+      </c>
+      <c r="X118" t="n">
+        <v>0.42447</v>
+      </c>
+      <c r="Y118" t="n">
+        <v>0.42284</v>
+      </c>
+      <c r="Z118" t="n">
+        <v>0.49769</v>
+      </c>
+      <c r="AA118" t="n">
+        <v>1.52058</v>
+      </c>
+      <c r="AB118" t="n">
+        <v>1.41375</v>
+      </c>
+      <c r="AC118" t="n">
+        <v>1.40572</v>
+      </c>
+      <c r="AD118" t="n">
+        <v>0.5393300000000001</v>
+      </c>
+      <c r="AE118" t="n">
+        <v>0.55301</v>
+      </c>
+      <c r="AF118" t="n">
+        <v>0.38516</v>
+      </c>
+      <c r="AG118" t="n">
+        <v>0.35019</v>
+      </c>
+      <c r="AH118" t="n">
+        <v>0.36929</v>
+      </c>
+      <c r="AI118" t="n">
+        <v>0.40248</v>
+      </c>
+      <c r="AJ118" t="n">
+        <v>0.49673</v>
+      </c>
+      <c r="AK118" t="n">
+        <v>0.33635</v>
+      </c>
+      <c r="AL118" t="n">
+        <v>0.26471</v>
+      </c>
+      <c r="AM118" t="n">
+        <v>0.35737</v>
+      </c>
+      <c r="AN118" t="n">
+        <v>-0.02913</v>
+      </c>
+      <c r="AO118" t="n">
+        <v>-0.03551</v>
+      </c>
+      <c r="AP118" t="n">
+        <v>0.30844</v>
+      </c>
+      <c r="AQ118" t="n">
+        <v>0.29885</v>
+      </c>
+      <c r="AR118" t="n">
+        <v>0.18652</v>
+      </c>
+      <c r="AS118" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AT118" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AU118" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AV118" t="n">
+        <v>-0.02382</v>
+      </c>
+      <c r="AW118" t="n">
+        <v>0.1027</v>
+      </c>
+      <c r="AX118" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AY118" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AZ118" t="n">
+        <v>0.4544</v>
+      </c>
+      <c r="BA118" t="n">
+        <v>0.43285</v>
+      </c>
+      <c r="BB118" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BC118" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BD118" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BE118" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BF118" t="n">
+        <v>0.5931799999999999</v>
+      </c>
+      <c r="BG118" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BH118" t="n">
+        <v>0.19531</v>
+      </c>
+      <c r="BI118" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BJ118" t="n">
+        <v>0.04271</v>
+      </c>
+      <c r="BK118" t="n">
+        <v>-0.03881</v>
+      </c>
+      <c r="BL118" t="n">
+        <v>0.01738</v>
+      </c>
+      <c r="BM118" t="n">
+        <v>0.32949</v>
+      </c>
+      <c r="BN118" t="n">
+        <v>0.37162</v>
+      </c>
+      <c r="BO118" t="n">
+        <v>0.60161</v>
+      </c>
+      <c r="BP118" t="n">
+        <v>0.76561</v>
+      </c>
+      <c r="BQ118" t="n">
+        <v>0.79339</v>
+      </c>
+      <c r="BR118" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BS118" t="n">
+        <v>1.18599</v>
+      </c>
+      <c r="BT118" t="n">
+        <v>1.3854</v>
+      </c>
+      <c r="BU118" t="n">
+        <v>1.13944</v>
+      </c>
+      <c r="BV118" t="n">
+        <v>0.85912</v>
+      </c>
+      <c r="BW118" t="n">
+        <v>1.22653</v>
+      </c>
+      <c r="BX118" t="n">
+        <v>1.12386</v>
+      </c>
+      <c r="BY118" t="n">
+        <v>1.12529</v>
+      </c>
+      <c r="BZ118" t="n">
+        <v>0.88205</v>
+      </c>
+      <c r="CA118" t="n">
+        <v>1.10811</v>
+      </c>
+      <c r="CB118" t="n">
+        <v>0.66732</v>
+      </c>
+      <c r="CC118" t="n">
+        <v>1.00143</v>
+      </c>
+      <c r="CD118" t="n">
+        <v>0.92653</v>
+      </c>
+      <c r="CE118" t="n">
+        <v>0.97805</v>
+      </c>
+      <c r="CF118" t="n">
+        <v>0.8115</v>
+      </c>
+      <c r="CG118" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="CH118" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="CI118" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CJ118" t="n">
+        <v>0.4545</v>
+      </c>
+      <c r="CK118" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="CL118" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="CM118" t="n">
+        <v>0.45419</v>
+      </c>
+      <c r="CN118" t="n">
+        <v>0.43238</v>
+      </c>
+      <c r="CO118" t="n">
+        <v>0.44822</v>
+      </c>
+      <c r="CP118" t="n">
+        <v>0.33393</v>
+      </c>
+      <c r="CQ118" t="n">
+        <v>0.37934</v>
+      </c>
+      <c r="CR118" t="n">
+        <v>0.35719</v>
+      </c>
+      <c r="CS118" t="n">
+        <v>0.33539</v>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" s="2" t="n">
+        <v>46140</v>
+      </c>
+      <c r="B119" t="n">
+        <v>0.32142</v>
+      </c>
+      <c r="C119" t="n">
+        <v>0.521</v>
+      </c>
+      <c r="D119" t="n">
+        <v>0.50008</v>
+      </c>
+      <c r="E119" t="n">
+        <v>0.49895</v>
+      </c>
+      <c r="F119" t="n">
+        <v>0.37176</v>
+      </c>
+      <c r="G119" t="n">
+        <v>0.45106</v>
+      </c>
+      <c r="H119" t="n">
+        <v>0.42016</v>
+      </c>
+      <c r="I119" t="n">
+        <v>0.37351</v>
+      </c>
+      <c r="J119" t="n">
+        <v>0.39503</v>
+      </c>
+      <c r="K119" t="n">
+        <v>0.38861</v>
+      </c>
+      <c r="L119" t="n">
+        <v>0.36743</v>
+      </c>
+      <c r="M119" t="n">
+        <v>0.43752</v>
+      </c>
+      <c r="N119" t="n">
+        <v>0.45453</v>
+      </c>
+      <c r="O119" t="n">
+        <v>0.33773</v>
+      </c>
+      <c r="P119" t="n">
+        <v>0.37506</v>
+      </c>
+      <c r="Q119" t="n">
+        <v>0.40325</v>
+      </c>
+      <c r="R119" t="n">
+        <v>0.37223</v>
+      </c>
+      <c r="S119" t="n">
+        <v>0.37275</v>
+      </c>
+      <c r="T119" t="n">
+        <v>0.35986</v>
+      </c>
+      <c r="U119" t="n">
+        <v>0.36582</v>
+      </c>
+      <c r="V119" t="n">
+        <v>0.35548</v>
+      </c>
+      <c r="W119" t="n">
+        <v>0.39863</v>
+      </c>
+      <c r="X119" t="n">
+        <v>0.37611</v>
+      </c>
+      <c r="Y119" t="n">
+        <v>0.3994</v>
+      </c>
+      <c r="Z119" t="n">
+        <v>0.40599</v>
+      </c>
+      <c r="AA119" t="n">
+        <v>0.48564</v>
+      </c>
+      <c r="AB119" t="n">
+        <v>0.4504</v>
+      </c>
+      <c r="AC119" t="n">
+        <v>0.44739</v>
+      </c>
+      <c r="AD119" t="n">
+        <v>0.34876</v>
+      </c>
+      <c r="AE119" t="n">
+        <v>0.40004</v>
+      </c>
+      <c r="AF119" t="n">
+        <v>0.35541</v>
+      </c>
+      <c r="AG119" t="n">
+        <v>0.3671</v>
+      </c>
+      <c r="AH119" t="n">
+        <v>0.34815</v>
+      </c>
+      <c r="AI119" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AJ119" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AK119" t="n">
+        <v>0.22189</v>
+      </c>
+      <c r="AL119" t="n">
+        <v>0.31534</v>
+      </c>
+      <c r="AM119" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AN119" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AO119" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AP119" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AQ119" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AR119" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AS119" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AT119" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AU119" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AV119" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AW119" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AX119" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AY119" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AZ119" t="n">
+        <v>-0.04413</v>
+      </c>
+      <c r="BA119" t="n">
+        <v>-0.04864</v>
+      </c>
+      <c r="BB119" t="n">
+        <v>0.37126</v>
+      </c>
+      <c r="BC119" t="n">
+        <v>-0.03264</v>
+      </c>
+      <c r="BD119" t="n">
+        <v>0.79632</v>
+      </c>
+      <c r="BE119" t="n">
+        <v>0.05294</v>
+      </c>
+      <c r="BF119" t="n">
+        <v>0.35699</v>
+      </c>
+      <c r="BG119" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BH119" t="n">
+        <v>0.35423</v>
+      </c>
+      <c r="BI119" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BJ119" t="n">
+        <v>0.44366</v>
+      </c>
+      <c r="BK119" t="n">
+        <v>0.38659</v>
+      </c>
+      <c r="BL119" t="n">
+        <v>0.43299</v>
+      </c>
+      <c r="BM119" t="n">
+        <v>0.37476</v>
+      </c>
+      <c r="BN119" t="n">
+        <v>0.36443</v>
+      </c>
+      <c r="BO119" t="n">
+        <v>0.45839</v>
+      </c>
+      <c r="BP119" t="n">
+        <v>0.3757</v>
+      </c>
+      <c r="BQ119" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BR119" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BS119" t="n">
+        <v>1.32025</v>
+      </c>
+      <c r="BT119" t="n">
+        <v>0.62813</v>
+      </c>
+      <c r="BU119" t="n">
+        <v>0.66576</v>
+      </c>
+      <c r="BV119" t="n">
+        <v>0.46949</v>
+      </c>
+      <c r="BW119" t="n">
+        <v>0.5072</v>
+      </c>
+      <c r="BX119" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BY119" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BZ119" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="CA119" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="CB119" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="CC119" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="CD119" t="n">
+        <v>0.43569</v>
+      </c>
+      <c r="CE119" t="n">
+        <v>0.50413</v>
+      </c>
+      <c r="CF119" t="n">
+        <v>0.6284</v>
+      </c>
+      <c r="CG119" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="CH119" t="n">
+        <v>0.41073</v>
+      </c>
+      <c r="CI119" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="CJ119" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="CK119" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="CL119" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="CM119" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="CN119" t="n">
+        <v>0.43649</v>
+      </c>
+      <c r="CO119" t="n">
+        <v>0.46165</v>
+      </c>
+      <c r="CP119" t="n">
+        <v>0.39982</v>
+      </c>
+      <c r="CQ119" t="n">
+        <v>0.36179</v>
+      </c>
+      <c r="CR119" t="n">
+        <v>0.35007</v>
+      </c>
+      <c r="CS119" t="n">
+        <v>0.34293</v>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" s="2" t="n">
+        <v>46141</v>
+      </c>
+      <c r="B120" t="n">
+        <v>0.31893</v>
+      </c>
+      <c r="C120" t="n">
+        <v>0.5229</v>
+      </c>
+      <c r="D120" t="n">
+        <v>0.5103</v>
+      </c>
+      <c r="E120" t="n">
+        <v>0.4446</v>
+      </c>
+      <c r="F120" t="n">
+        <v>0.397</v>
+      </c>
+      <c r="G120" t="n">
+        <v>0.39589</v>
+      </c>
+      <c r="H120" t="n">
+        <v>0.40035</v>
+      </c>
+      <c r="I120" t="n">
+        <v>0.3726</v>
+      </c>
+      <c r="J120" t="n">
+        <v>0.36402</v>
+      </c>
+      <c r="K120" t="n">
+        <v>0.39631</v>
+      </c>
+      <c r="L120" t="n">
+        <v>0.39374</v>
+      </c>
+      <c r="M120" t="n">
+        <v>0.36882</v>
+      </c>
+      <c r="N120" t="n">
+        <v>0.45869</v>
+      </c>
+      <c r="O120" t="n">
+        <v>0.3664</v>
+      </c>
+      <c r="P120" t="n">
+        <v>0.35334</v>
+      </c>
+      <c r="Q120" t="n">
+        <v>0.37068</v>
+      </c>
+      <c r="R120" t="n">
+        <v>0.36338</v>
+      </c>
+      <c r="S120" t="n">
+        <v>0.36491</v>
+      </c>
+      <c r="T120" t="n">
+        <v>0.34107</v>
+      </c>
+      <c r="U120" t="n">
+        <v>0.33853</v>
+      </c>
+      <c r="V120" t="n">
+        <v>0.33547</v>
+      </c>
+      <c r="W120" t="n">
+        <v>0.3386</v>
+      </c>
+      <c r="X120" t="n">
+        <v>0.3343</v>
+      </c>
+      <c r="Y120" t="n">
+        <v>0.35258</v>
+      </c>
+      <c r="Z120" t="n">
+        <v>0.34131</v>
+      </c>
+      <c r="AA120" t="n">
+        <v>0.35493</v>
+      </c>
+      <c r="AB120" t="n">
+        <v>0.3924</v>
+      </c>
+      <c r="AC120" t="n">
+        <v>0.39404</v>
+      </c>
+      <c r="AD120" t="n">
+        <v>0.3539</v>
+      </c>
+      <c r="AE120" t="n">
+        <v>0.38143</v>
+      </c>
+      <c r="AF120" t="n">
+        <v>0.34699</v>
+      </c>
+      <c r="AG120" t="n">
+        <v>0.39831</v>
+      </c>
+      <c r="AH120" t="n">
+        <v>0.42204</v>
+      </c>
+      <c r="AI120" t="n">
+        <v>0.43635</v>
+      </c>
+      <c r="AJ120" t="n">
+        <v>0.35841</v>
+      </c>
+      <c r="AK120" t="n">
+        <v>0.41567</v>
+      </c>
+      <c r="AL120" t="n">
+        <v>0.34204</v>
+      </c>
+      <c r="AM120" t="n">
+        <v>0.354</v>
+      </c>
+      <c r="AN120" t="n">
+        <v>-0.03397</v>
+      </c>
+      <c r="AO120" t="n">
+        <v>-0.04075</v>
+      </c>
+      <c r="AP120" t="n">
+        <v>-0.04609000000000001</v>
+      </c>
+      <c r="AQ120" t="n">
+        <v>0.3029</v>
+      </c>
+      <c r="AR120" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AS120" t="n">
+        <v>0.32296</v>
+      </c>
+      <c r="AT120" t="n">
+        <v>0.5915499999999999</v>
+      </c>
+      <c r="AU120" t="n">
+        <v>0.28265</v>
+      </c>
+      <c r="AV120" t="n">
+        <v>0.40207</v>
+      </c>
+      <c r="AW120" t="n">
+        <v>0.31266</v>
+      </c>
+      <c r="AX120" t="n">
+        <v>0.21235</v>
+      </c>
+      <c r="AY120" t="n">
+        <v>0.18459</v>
+      </c>
+      <c r="AZ120" t="n">
+        <v>0.27659</v>
+      </c>
+      <c r="BA120" t="n">
+        <v>0.34277</v>
+      </c>
+      <c r="BB120" t="n">
+        <v>0.36596</v>
+      </c>
+      <c r="BC120" t="n">
+        <v>0.30644</v>
+      </c>
+      <c r="BD120" t="n">
+        <v>0.40682</v>
+      </c>
+      <c r="BE120" t="n">
+        <v>0.6411399999999999</v>
+      </c>
+      <c r="BF120" t="n">
+        <v>0.32463</v>
+      </c>
+      <c r="BG120" t="n">
+        <v>0.30073</v>
+      </c>
+      <c r="BH120" t="n">
+        <v>0.31364</v>
+      </c>
+      <c r="BI120" t="n">
+        <v>0.34216</v>
+      </c>
+      <c r="BJ120" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BK120" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BL120" t="n">
+        <v>0.41156</v>
+      </c>
+      <c r="BM120" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BN120" t="n">
+        <v>0.32597</v>
+      </c>
+      <c r="BO120" t="n">
+        <v>0.33107</v>
+      </c>
+      <c r="BP120" t="n">
+        <v>0.44193</v>
+      </c>
+      <c r="BQ120" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BR120" t="n">
+        <v>0.47413</v>
+      </c>
+      <c r="BS120" t="n">
+        <v>0.52606</v>
+      </c>
+      <c r="BT120" t="n">
+        <v>0.45115</v>
+      </c>
+      <c r="BU120" t="n">
+        <v>0.47415</v>
+      </c>
+      <c r="BV120" t="n">
+        <v>0.40416</v>
+      </c>
+      <c r="BW120" t="n">
+        <v>0.3609</v>
+      </c>
+      <c r="BX120" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BY120" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BZ120" t="n">
+        <v>0.33401</v>
+      </c>
+      <c r="CA120" t="n">
+        <v>0.45615</v>
+      </c>
+      <c r="CB120" t="n">
+        <v>0.52154</v>
+      </c>
+      <c r="CC120" t="n">
+        <v>0.4935</v>
+      </c>
+      <c r="CD120" t="n">
+        <v>0.5046499999999999</v>
+      </c>
+      <c r="CE120" t="n">
+        <v>0.44615</v>
+      </c>
+      <c r="CF120" t="n">
+        <v>0.42377</v>
+      </c>
+      <c r="CG120" t="n">
+        <v>0.41586</v>
+      </c>
+      <c r="CH120" t="n">
+        <v>0.42761</v>
+      </c>
+      <c r="CI120" t="n">
+        <v>0.35506</v>
+      </c>
+      <c r="CJ120" t="n">
+        <v>0.3728</v>
+      </c>
+      <c r="CK120" t="n">
+        <v>0.34918</v>
+      </c>
+      <c r="CL120" t="n">
+        <v>0.34485</v>
+      </c>
+      <c r="CM120" t="n">
+        <v>0.31995</v>
+      </c>
+      <c r="CN120" t="n">
+        <v>0.32425</v>
+      </c>
+      <c r="CO120" t="n">
+        <v>0.32121</v>
+      </c>
+      <c r="CP120" t="n">
+        <v>0.3126</v>
+      </c>
+      <c r="CQ120" t="n">
+        <v>0.31924</v>
+      </c>
+      <c r="CR120" t="n">
+        <v>0.32194</v>
+      </c>
+      <c r="CS120" t="n">
+        <v>0.33045</v>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" s="2" t="n">
+        <v>46142</v>
+      </c>
+      <c r="B121" t="n">
+        <v>0.3051</v>
+      </c>
+      <c r="C121" t="n">
+        <v>0.36693</v>
+      </c>
+      <c r="D121" t="n">
+        <v>0.3431</v>
+      </c>
+      <c r="E121" t="n">
+        <v>0.37991</v>
+      </c>
+      <c r="F121" t="n">
+        <v>0.35796</v>
+      </c>
+      <c r="G121" t="n">
+        <v>0.33849</v>
+      </c>
+      <c r="H121" t="n">
+        <v>0.32643</v>
+      </c>
+      <c r="I121" t="n">
+        <v>0.3271</v>
+      </c>
+      <c r="J121" t="n">
+        <v>0.32996</v>
+      </c>
+      <c r="K121" t="n">
+        <v>0.32008</v>
+      </c>
+      <c r="L121" t="n">
+        <v>0.31864</v>
+      </c>
+      <c r="M121" t="n">
+        <v>0.31548</v>
+      </c>
+      <c r="N121" t="n">
+        <v>0.31756</v>
+      </c>
+      <c r="O121" t="n">
+        <v>0.31894</v>
+      </c>
+      <c r="P121" t="n">
+        <v>0.31511</v>
+      </c>
+      <c r="Q121" t="n">
+        <v>0.31727</v>
+      </c>
+      <c r="R121" t="n">
+        <v>0.31074</v>
+      </c>
+      <c r="S121" t="n">
+        <v>0.31211</v>
+      </c>
+      <c r="T121" t="n">
+        <v>0.31664</v>
+      </c>
+      <c r="U121" t="n">
+        <v>0.31545</v>
+      </c>
+      <c r="V121" t="n">
+        <v>0.30897</v>
+      </c>
+      <c r="W121" t="n">
+        <v>0.30841</v>
+      </c>
+      <c r="X121" t="n">
+        <v>0.31319</v>
+      </c>
+      <c r="Y121" t="n">
+        <v>0.31434</v>
+      </c>
+      <c r="Z121" t="n">
+        <v>0.31646</v>
+      </c>
+      <c r="AA121" t="n">
+        <v>0.32452</v>
+      </c>
+      <c r="AB121" t="n">
+        <v>0.32434</v>
+      </c>
+      <c r="AC121" t="n">
+        <v>0.33259</v>
+      </c>
+      <c r="AD121" t="n">
+        <v>0.32612</v>
+      </c>
+      <c r="AE121" t="n">
+        <v>0.31711</v>
+      </c>
+      <c r="AF121" t="n">
+        <v>0.31638</v>
+      </c>
+      <c r="AG121" t="n">
+        <v>0.29227</v>
+      </c>
+      <c r="AH121" t="n">
+        <v>0.30537</v>
+      </c>
+      <c r="AI121" t="n">
+        <v>0.29483</v>
+      </c>
+      <c r="AJ121" t="n">
+        <v>0.28505</v>
+      </c>
+      <c r="AK121" t="n">
+        <v>0.2865</v>
+      </c>
+      <c r="AL121" t="n">
+        <v>0.30436</v>
+      </c>
+      <c r="AM121" t="n">
+        <v>0.29906</v>
+      </c>
+      <c r="AN121" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AO121" t="n">
+        <v>0.31899</v>
+      </c>
+      <c r="AP121" t="n">
+        <v>0.30383</v>
+      </c>
+      <c r="AQ121" t="n">
+        <v>0.27003</v>
+      </c>
+      <c r="AR121" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AS121" t="n">
+        <v>0.26146</v>
+      </c>
+      <c r="AT121" t="n">
+        <v>0.07856</v>
+      </c>
+      <c r="AU121" t="n">
+        <v>-0.04403</v>
+      </c>
+      <c r="AV121" t="n">
+        <v>0.13228</v>
+      </c>
+      <c r="AW121" t="n">
+        <v>-0.04207</v>
+      </c>
+      <c r="AX121" t="n">
+        <v>-0.03713</v>
+      </c>
+      <c r="AY121" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AZ121" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BA121" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BB121" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BC121" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BD121" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BE121" t="n">
+        <v>0.06473999999999999</v>
+      </c>
+      <c r="BF121" t="n">
+        <v>0.0664</v>
+      </c>
+      <c r="BG121" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BH121" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BI121" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BJ121" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BK121" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BL121" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BM121" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BN121" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BO121" t="n">
+        <v>0.2341</v>
+      </c>
+      <c r="BP121" t="n">
+        <v>0.29636</v>
+      </c>
+      <c r="BQ121" t="n">
+        <v>0.29898</v>
+      </c>
+      <c r="BR121" t="n">
+        <v>0.3081</v>
+      </c>
+      <c r="BS121" t="n">
+        <v>0.29577</v>
+      </c>
+      <c r="BT121" t="n">
+        <v>0.30256</v>
+      </c>
+      <c r="BU121" t="n">
+        <v>0.31995</v>
+      </c>
+      <c r="BV121" t="n">
+        <v>0.32957</v>
+      </c>
+      <c r="BW121" t="n">
+        <v>0.31545</v>
+      </c>
+      <c r="BX121" t="n">
+        <v>0.33545</v>
+      </c>
+      <c r="BY121" t="n">
+        <v>0.3357</v>
+      </c>
+      <c r="BZ121" t="n">
+        <v>0.33583</v>
+      </c>
+      <c r="CA121" t="n">
+        <v>0.293</v>
+      </c>
+      <c r="CB121" t="n">
+        <v>0.14278</v>
+      </c>
+      <c r="CC121" t="n">
+        <v>0.17522</v>
+      </c>
+      <c r="CD121" t="n">
+        <v>0.15212</v>
+      </c>
+      <c r="CE121" t="n">
+        <v>0.24618</v>
+      </c>
+      <c r="CF121" t="n">
+        <v>0.30189</v>
+      </c>
+      <c r="CG121" t="n">
+        <v>0.15504</v>
+      </c>
+      <c r="CH121" t="n">
+        <v>0.21917</v>
+      </c>
+      <c r="CI121" t="n">
+        <v>0.20197</v>
+      </c>
+      <c r="CJ121" t="n">
+        <v>0.33012</v>
+      </c>
+      <c r="CK121" t="n">
+        <v>0.28506</v>
+      </c>
+      <c r="CL121" t="n">
+        <v>0.25743</v>
+      </c>
+      <c r="CM121" t="n">
+        <v>0.21901</v>
+      </c>
+      <c r="CN121" t="n">
+        <v>0.15579</v>
+      </c>
+      <c r="CO121" t="n">
+        <v>0.29476</v>
+      </c>
+      <c r="CP121" t="n">
+        <v>0.32704</v>
+      </c>
+      <c r="CQ121" t="n">
+        <v>0.33543</v>
+      </c>
+      <c r="CR121" t="n">
+        <v>0.32836</v>
+      </c>
+      <c r="CS121" t="n">
+        <v>0.19443</v>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" s="2" t="n">
+        <v>46143</v>
+      </c>
+      <c r="B122" t="n">
+        <v>0.37592</v>
+      </c>
+      <c r="C122" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="D122" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="E122" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="F122" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="G122" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="H122" t="n">
+        <v>0.22812</v>
+      </c>
+      <c r="I122" t="n">
+        <v>0.0291</v>
+      </c>
+      <c r="J122" t="n">
+        <v>0.21838</v>
+      </c>
+      <c r="K122" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="L122" t="n">
+        <v>0.17884</v>
+      </c>
+      <c r="M122" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="N122" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="O122" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="P122" t="n">
+        <v>0.20819</v>
+      </c>
+      <c r="Q122" t="n">
+        <v>0.2138</v>
+      </c>
+      <c r="R122" t="n">
+        <v>0.19602</v>
+      </c>
+      <c r="S122" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="T122" t="n">
+        <v>-0.04944</v>
+      </c>
+      <c r="U122" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="V122" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="W122" t="n">
+        <v>0.16974</v>
+      </c>
+      <c r="X122" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="Y122" t="n">
+        <v>0.19632</v>
+      </c>
+      <c r="Z122" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AA122" t="n">
+        <v>-0.01855</v>
+      </c>
+      <c r="AB122" t="n">
+        <v>0.21301</v>
+      </c>
+      <c r="AC122" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AD122" t="n">
+        <v>0.0892</v>
+      </c>
+      <c r="AE122" t="n">
+        <v>0.10251</v>
+      </c>
+      <c r="AF122" t="n">
+        <v>0.10148</v>
+      </c>
+      <c r="AG122" t="n">
+        <v>0.04278</v>
+      </c>
+      <c r="AH122" t="n">
+        <v>-0.04697999999999999</v>
+      </c>
+      <c r="AI122" t="n">
+        <v>-0.04575</v>
+      </c>
+      <c r="AJ122" t="n">
+        <v>-0.04621</v>
+      </c>
+      <c r="AK122" t="n">
+        <v>-0.04409</v>
+      </c>
+      <c r="AL122" t="n">
+        <v>-0.04621</v>
+      </c>
+      <c r="AM122" t="n">
+        <v>-0.04489</v>
+      </c>
+      <c r="AN122" t="n">
+        <v>-0.04398</v>
+      </c>
+      <c r="AO122" t="n">
+        <v>0.2944</v>
+      </c>
+      <c r="AP122" t="n">
+        <v>0.00596</v>
+      </c>
+      <c r="AQ122" t="n">
+        <v>0.19847</v>
+      </c>
+      <c r="AR122" t="n">
+        <v>0.04541</v>
+      </c>
+      <c r="AS122" t="n">
+        <v>0.264</v>
+      </c>
+      <c r="AT122" t="n">
+        <v>0.14076</v>
+      </c>
+      <c r="AU122" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AV122" t="n">
+        <v>-0.04392</v>
+      </c>
+      <c r="AW122" t="n">
+        <v>-0.04394</v>
+      </c>
+      <c r="AX122" t="n">
+        <v>-0.04574</v>
+      </c>
+      <c r="AY122" t="n">
+        <v>-0.0456</v>
+      </c>
+      <c r="AZ122" t="n">
+        <v>-0.04561</v>
+      </c>
+      <c r="BA122" t="n">
+        <v>-0.04369</v>
+      </c>
+      <c r="BB122" t="n">
+        <v>-0.04335</v>
+      </c>
+      <c r="BC122" t="n">
+        <v>-0.04548</v>
+      </c>
+      <c r="BD122" t="n">
+        <v>-0.04338</v>
+      </c>
+      <c r="BE122" t="n">
+        <v>-0.01024</v>
+      </c>
+      <c r="BF122" t="n">
+        <v>-0.0453</v>
+      </c>
+      <c r="BG122" t="n">
+        <v>-0.04525</v>
+      </c>
+      <c r="BH122" t="n">
+        <v>-0.04537</v>
+      </c>
+      <c r="BI122" t="n">
+        <v>-0.04358</v>
+      </c>
+      <c r="BJ122" t="n">
+        <v>-0.04422</v>
+      </c>
+      <c r="BK122" t="n">
+        <v>0.05262</v>
+      </c>
+      <c r="BL122" t="n">
+        <v>0.0508</v>
+      </c>
+      <c r="BM122" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BN122" t="n">
+        <v>-0.04471</v>
+      </c>
+      <c r="BO122" t="n">
+        <v>-0.04997</v>
+      </c>
+      <c r="BP122" t="n">
+        <v>-0.04985</v>
+      </c>
+      <c r="BQ122" t="n">
+        <v>-0.0474</v>
+      </c>
+      <c r="BR122" t="n">
+        <v>-0.04790999999999999</v>
+      </c>
+      <c r="BS122" t="n">
+        <v>0.19975</v>
+      </c>
+      <c r="BT122" t="n">
+        <v>0.14272</v>
+      </c>
+      <c r="BU122" t="n">
+        <v>0.28993</v>
+      </c>
+      <c r="BV122" t="n">
+        <v>0.29465</v>
+      </c>
+      <c r="BW122" t="n">
+        <v>0.30453</v>
+      </c>
+      <c r="BX122" t="n">
+        <v>0.29982</v>
+      </c>
+      <c r="BY122" t="n">
+        <v>0.29492</v>
+      </c>
+      <c r="BZ122" t="n">
+        <v>0.29281</v>
+      </c>
+      <c r="CA122" t="n">
+        <v>0.29328</v>
+      </c>
+      <c r="CB122" t="n">
+        <v>0.29225</v>
+      </c>
+      <c r="CC122" t="n">
+        <v>0.29677</v>
+      </c>
+      <c r="CD122" t="n">
+        <v>0.29074</v>
+      </c>
+      <c r="CE122" t="n">
+        <v>0.29497</v>
+      </c>
+      <c r="CF122" t="n">
+        <v>0.26875</v>
+      </c>
+      <c r="CG122" t="n">
+        <v>0.29381</v>
+      </c>
+      <c r="CH122" t="n">
+        <v>0.29802</v>
+      </c>
+      <c r="CI122" t="n">
+        <v>0.30854</v>
+      </c>
+      <c r="CJ122" t="n">
+        <v>0.30375</v>
+      </c>
+      <c r="CK122" t="n">
+        <v>0.30221</v>
+      </c>
+      <c r="CL122" t="n">
+        <v>0.31434</v>
+      </c>
+      <c r="CM122" t="n">
+        <v>0.31838</v>
+      </c>
+      <c r="CN122" t="n">
+        <v>0.34196</v>
+      </c>
+      <c r="CO122" t="n">
+        <v>0.30222</v>
+      </c>
+      <c r="CP122" t="n">
+        <v>0.25601</v>
+      </c>
+      <c r="CQ122" t="n">
+        <v>0.24108</v>
+      </c>
+      <c r="CR122" t="n">
+        <v>0.26285</v>
+      </c>
+      <c r="CS122" t="n">
+        <v>0.24425</v>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" s="2" t="n">
+        <v>46144</v>
+      </c>
+      <c r="B123" t="n">
+        <v>0.19948</v>
+      </c>
+      <c r="C123" t="n">
+        <v>1.33541</v>
+      </c>
+      <c r="D123" t="n">
+        <v>0.31055</v>
+      </c>
+      <c r="E123" t="n">
+        <v>0.20296</v>
+      </c>
+      <c r="F123" t="n">
+        <v>0.2439</v>
+      </c>
+      <c r="G123" t="n">
+        <v>0.31441</v>
+      </c>
+      <c r="H123" t="n">
+        <v>0.30705</v>
+      </c>
+      <c r="I123" t="n">
+        <v>0.31463</v>
+      </c>
+      <c r="J123" t="n">
+        <v>0.30134</v>
+      </c>
+      <c r="K123" t="n">
+        <v>0.28114</v>
+      </c>
+      <c r="L123" t="n">
+        <v>0.29442</v>
+      </c>
+      <c r="M123" t="n">
+        <v>0.29069</v>
+      </c>
+      <c r="N123" t="n">
+        <v>0.28802</v>
+      </c>
+      <c r="O123" t="n">
+        <v>0.28084</v>
+      </c>
+      <c r="P123" t="n">
+        <v>0.27116</v>
+      </c>
+      <c r="Q123" t="n">
+        <v>0.27089</v>
+      </c>
+      <c r="R123" t="n">
+        <v>0.2810299999999999</v>
+      </c>
+      <c r="S123" t="n">
+        <v>0.17236</v>
+      </c>
+      <c r="T123" t="n">
+        <v>0.1586</v>
+      </c>
+      <c r="U123" t="n">
+        <v>0.17092</v>
+      </c>
+      <c r="V123" t="n">
+        <v>0.1477</v>
+      </c>
+      <c r="W123" t="n">
+        <v>0.15943</v>
+      </c>
+      <c r="X123" t="n">
+        <v>0.15858</v>
+      </c>
+      <c r="Y123" t="n">
+        <v>0.23612</v>
+      </c>
+      <c r="Z123" t="n">
+        <v>0.214</v>
+      </c>
+      <c r="AA123" t="n">
+        <v>0.22651</v>
+      </c>
+      <c r="AB123" t="n">
+        <v>0.26883</v>
+      </c>
+      <c r="AC123" t="n">
+        <v>0.28566</v>
+      </c>
+      <c r="AD123" t="n">
+        <v>0.29075</v>
+      </c>
+      <c r="AE123" t="n">
+        <v>0.31932</v>
+      </c>
+      <c r="AF123" t="n">
+        <v>0.28069</v>
+      </c>
+      <c r="AG123" t="n">
+        <v>0.28084</v>
+      </c>
+      <c r="AH123" t="n">
+        <v>0.2810299999999999</v>
+      </c>
+      <c r="AI123" t="n">
+        <v>0.28043</v>
+      </c>
+      <c r="AJ123" t="n">
+        <v>0.27068</v>
+      </c>
+      <c r="AK123" t="n">
+        <v>0.28091</v>
+      </c>
+      <c r="AL123" t="n">
+        <v>0.32236</v>
+      </c>
+      <c r="AM123" t="n">
+        <v>0.31015</v>
+      </c>
+      <c r="AN123" t="n">
+        <v>0.30493</v>
+      </c>
+      <c r="AO123" t="n">
+        <v>0.3163</v>
+      </c>
+      <c r="AP123" t="n">
+        <v>0.30938</v>
+      </c>
+      <c r="AQ123" t="n">
+        <v>0.35894</v>
+      </c>
+      <c r="AR123" t="n">
+        <v>0.31624</v>
+      </c>
+      <c r="AS123" t="n">
+        <v>0.29725</v>
+      </c>
+      <c r="AT123" t="n">
+        <v>0.35101</v>
+      </c>
+      <c r="AU123" t="n">
+        <v>0.38145</v>
+      </c>
+      <c r="AV123" t="n">
+        <v>0.43073</v>
+      </c>
+      <c r="AW123" t="n">
+        <v>0.46068</v>
+      </c>
+      <c r="AX123" t="n">
+        <v>0.33181</v>
+      </c>
+      <c r="AY123" t="n">
+        <v>0.41842</v>
+      </c>
+      <c r="AZ123" t="n">
+        <v>0.41525</v>
+      </c>
+      <c r="BA123" t="n">
+        <v>0.39871</v>
+      </c>
+      <c r="BB123" t="n">
+        <v>0.4024</v>
+      </c>
+      <c r="BC123" t="n">
+        <v>0.30005</v>
+      </c>
+      <c r="BD123" t="n">
+        <v>0.30095</v>
+      </c>
+      <c r="BE123" t="n">
+        <v>0.29929</v>
+      </c>
+      <c r="BF123" t="n">
+        <v>0.29998</v>
+      </c>
+      <c r="BG123" t="n">
+        <v>0.15655</v>
+      </c>
+      <c r="BH123" t="n">
+        <v>0.29425</v>
+      </c>
+      <c r="BI123" t="n">
+        <v>0.31093</v>
+      </c>
+      <c r="BJ123" t="n">
+        <v>0.31342</v>
+      </c>
+      <c r="BK123" t="n">
+        <v>0.31265</v>
+      </c>
+      <c r="BL123" t="n">
+        <v>0.32184</v>
+      </c>
+      <c r="BM123" t="n">
+        <v>0.34626</v>
+      </c>
+      <c r="BN123" t="n">
+        <v>0.30066</v>
+      </c>
+      <c r="BO123" t="n">
+        <v>0.33082</v>
+      </c>
+      <c r="BP123" t="n">
+        <v>0.38545</v>
+      </c>
+      <c r="BQ123" t="n">
+        <v>0.47916</v>
+      </c>
+      <c r="BR123" t="n">
+        <v>0.5076700000000001</v>
+      </c>
+      <c r="BS123" t="n">
+        <v>0.79098</v>
+      </c>
+      <c r="BT123" t="n">
+        <v>0.6220399999999999</v>
+      </c>
+      <c r="BU123" t="n">
+        <v>0.7857499999999999</v>
+      </c>
+      <c r="BV123" t="n">
+        <v>0.40003</v>
+      </c>
+      <c r="BW123" t="n">
+        <v>0.49797</v>
+      </c>
+      <c r="BX123" t="n">
+        <v>0.7810199999999999</v>
+      </c>
+      <c r="BY123" t="n">
+        <v>0.92038</v>
+      </c>
+      <c r="BZ123" t="n">
+        <v>0.49455</v>
+      </c>
+      <c r="CA123" t="n">
+        <v>0.9141900000000001</v>
+      </c>
+      <c r="CB123" t="n">
+        <v>0.86286</v>
+      </c>
+      <c r="CC123" t="n">
+        <v>1.29619</v>
+      </c>
+      <c r="CD123" t="n">
+        <v>0.35362</v>
+      </c>
+      <c r="CE123" t="n">
+        <v>0.88747</v>
+      </c>
+      <c r="CF123" t="n">
+        <v>0.63159</v>
+      </c>
+      <c r="CG123" t="n">
+        <v>1.18705</v>
+      </c>
+      <c r="CH123" t="n">
+        <v>0.86975</v>
+      </c>
+      <c r="CI123" t="n">
+        <v>0.61442</v>
+      </c>
+      <c r="CJ123" t="n">
+        <v>1.33081</v>
+      </c>
+      <c r="CK123" t="n">
+        <v>1.03289</v>
+      </c>
+      <c r="CL123" t="n">
+        <v>0.5307500000000001</v>
+      </c>
+      <c r="CM123" t="n">
+        <v>0.79096</v>
+      </c>
+      <c r="CN123" t="n">
+        <v>0.55647</v>
+      </c>
+      <c r="CO123" t="n">
+        <v>0.77295</v>
+      </c>
+      <c r="CP123" t="n">
+        <v>0.77752</v>
+      </c>
+      <c r="CQ123" t="n">
+        <v>0.8767699999999999</v>
+      </c>
+      <c r="CR123" t="n">
+        <v>0.87385</v>
+      </c>
+      <c r="CS123" t="n">
+        <v>0.49312</v>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" s="2" t="n">
+        <v>46145</v>
+      </c>
+      <c r="B124" t="n">
+        <v>0.39865</v>
+      </c>
+      <c r="C124" t="n">
+        <v>1.39985</v>
+      </c>
+      <c r="D124" t="n">
+        <v>0.44991</v>
+      </c>
+      <c r="E124" t="n">
+        <v>1.20696</v>
+      </c>
+      <c r="F124" t="n">
+        <v>0.87882</v>
+      </c>
+      <c r="G124" t="n">
+        <v>0.55101</v>
+      </c>
+      <c r="H124" t="n">
+        <v>0.62181</v>
+      </c>
+      <c r="I124" t="n">
+        <v>0.53831</v>
+      </c>
+      <c r="J124" t="n">
+        <v>0.49768</v>
+      </c>
+      <c r="K124" t="n">
+        <v>0.45581</v>
+      </c>
+      <c r="L124" t="n">
+        <v>0.42425</v>
+      </c>
+      <c r="M124" t="n">
+        <v>0.43713</v>
+      </c>
+      <c r="N124" t="n">
+        <v>0.45136</v>
+      </c>
+      <c r="O124" t="n">
+        <v>0.38816</v>
+      </c>
+      <c r="P124" t="n">
+        <v>0.45268</v>
+      </c>
+      <c r="Q124" t="n">
+        <v>0.42035</v>
+      </c>
+      <c r="R124" t="n">
+        <v>0.24167</v>
+      </c>
+      <c r="S124" t="n">
+        <v>0.36672</v>
+      </c>
+      <c r="T124" t="n">
+        <v>0.31047</v>
+      </c>
+      <c r="U124" t="n">
+        <v>0.35206</v>
+      </c>
+      <c r="V124" t="n">
+        <v>0.28847</v>
+      </c>
+      <c r="W124" t="n">
+        <v>0.26916</v>
+      </c>
+      <c r="X124" t="n">
+        <v>0.2508</v>
+      </c>
+      <c r="Y124" t="n">
+        <v>0.31752</v>
+      </c>
+      <c r="Z124" t="n">
+        <v>0.24438</v>
+      </c>
+      <c r="AA124" t="n">
+        <v>0.2782</v>
+      </c>
+      <c r="AB124" t="n">
+        <v>0.27848</v>
+      </c>
+      <c r="AC124" t="n">
+        <v>0.23886</v>
+      </c>
+      <c r="AD124" t="n">
+        <v>-0.00399</v>
+      </c>
+      <c r="AE124" t="n">
+        <v>0.34743</v>
+      </c>
+      <c r="AF124" t="n">
+        <v>0.41799</v>
+      </c>
+      <c r="AG124" t="n">
+        <v>0.19894</v>
+      </c>
+      <c r="AH124" t="n">
+        <v>0.23107</v>
+      </c>
+      <c r="AI124" t="n">
+        <v>0.03671</v>
+      </c>
+      <c r="AJ124" t="n">
+        <v>-0.02642</v>
+      </c>
+      <c r="AK124" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AL124" t="n">
+        <v>0.37721</v>
+      </c>
+      <c r="AM124" t="n">
+        <v>0.14521</v>
+      </c>
+      <c r="AN124" t="n">
+        <v>0.8916799999999999</v>
+      </c>
+      <c r="AO124" t="n">
+        <v>0.4767</v>
+      </c>
+      <c r="AP124" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AQ124" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AR124" t="n">
+        <v>0.11075</v>
+      </c>
+      <c r="AS124" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AT124" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AU124" t="n">
+        <v>0.7771699999999999</v>
+      </c>
+      <c r="AV124" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AW124" t="n">
+        <v>0.87503</v>
+      </c>
+      <c r="AX124" t="n">
+        <v>0.2657</v>
+      </c>
+      <c r="AY124" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AZ124" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BA124" t="n">
+        <v>0.26632</v>
+      </c>
+      <c r="BB124" t="n">
+        <v>0.2417</v>
+      </c>
+      <c r="BC124" t="n">
+        <v>0.14056</v>
+      </c>
+      <c r="BD124" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BE124" t="n">
+        <v>0.60178</v>
+      </c>
+      <c r="BF124" t="n">
+        <v>0.41223</v>
+      </c>
+      <c r="BG124" t="n">
+        <v>0.3105</v>
+      </c>
+      <c r="BH124" t="n">
+        <v>0.2751</v>
+      </c>
+      <c r="BI124" t="n">
+        <v>0.28783</v>
+      </c>
+      <c r="BJ124" t="n">
+        <v>0.3209</v>
+      </c>
+      <c r="BK124" t="n">
+        <v>0.40649</v>
+      </c>
+      <c r="BL124" t="n">
+        <v>0.27089</v>
+      </c>
+      <c r="BM124" t="n">
+        <v>0.30444</v>
+      </c>
+      <c r="BN124" t="n">
+        <v>0.31953</v>
+      </c>
+      <c r="BO124" t="n">
+        <v>0.31821</v>
+      </c>
+      <c r="BP124" t="n">
+        <v>0.29108</v>
+      </c>
+      <c r="BQ124" t="n">
+        <v>0.15956</v>
+      </c>
+      <c r="BR124" t="n">
+        <v>0.30016</v>
+      </c>
+      <c r="BS124" t="n">
+        <v>0.17607</v>
+      </c>
+      <c r="BT124" t="n">
+        <v>0.26461</v>
+      </c>
+      <c r="BU124" t="n">
+        <v>0.25534</v>
+      </c>
+      <c r="BV124" t="n">
+        <v>0.29596</v>
+      </c>
+      <c r="BW124" t="n">
+        <v>0.29146</v>
+      </c>
+      <c r="BX124" t="n">
+        <v>0.22588</v>
+      </c>
+      <c r="BY124" t="n">
+        <v>0.28072</v>
+      </c>
+      <c r="BZ124" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="CA124" t="n">
+        <v>0.08868000000000001</v>
+      </c>
+      <c r="CB124" t="n">
+        <v>0.06897</v>
+      </c>
+      <c r="CC124" t="n">
+        <v>0.11125</v>
+      </c>
+      <c r="CD124" t="n">
+        <v>0.03629</v>
+      </c>
+      <c r="CE124" t="n">
+        <v>0.12232</v>
+      </c>
+      <c r="CF124" t="n">
+        <v>0.21532</v>
+      </c>
+      <c r="CG124" t="n">
+        <v>0.11422</v>
+      </c>
+      <c r="CH124" t="n">
+        <v>0.20126</v>
+      </c>
+      <c r="CI124" t="n">
+        <v>0.19916</v>
+      </c>
+      <c r="CJ124" t="n">
+        <v>0.19145</v>
+      </c>
+      <c r="CK124" t="n">
+        <v>0.13512</v>
+      </c>
+      <c r="CL124" t="n">
+        <v>0.13914</v>
+      </c>
+      <c r="CM124" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="CN124" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="CO124" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="CP124" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="CQ124" t="n">
+        <v>-0.008840000000000001</v>
+      </c>
+      <c r="CR124" t="n">
+        <v>-0.01897</v>
+      </c>
+      <c r="CS124" t="n">
+        <v>0.21447</v>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" s="2" t="n">
+        <v>46146</v>
+      </c>
+      <c r="B125" t="n">
+        <v>0.32836</v>
+      </c>
+      <c r="C125" t="n">
+        <v>0.77626</v>
+      </c>
+      <c r="D125" t="n">
+        <v>0.11568</v>
+      </c>
+      <c r="E125" t="n">
+        <v>-0.00694</v>
+      </c>
+      <c r="F125" t="n">
+        <v>-0.0385</v>
+      </c>
+      <c r="G125" t="n">
+        <v>0.05835</v>
+      </c>
+      <c r="H125" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="I125" t="n">
+        <v>0.06136999999999999</v>
+      </c>
+      <c r="J125" t="n">
+        <v>-0.03879</v>
+      </c>
+      <c r="K125" t="n">
+        <v>0.16195</v>
+      </c>
+      <c r="L125" t="n">
+        <v>0.13083</v>
+      </c>
+      <c r="M125" t="n">
+        <v>0.15272</v>
+      </c>
+      <c r="N125" t="n">
+        <v>0.17454</v>
+      </c>
+      <c r="O125" t="n">
+        <v>0.10046</v>
+      </c>
+      <c r="P125" t="n">
+        <v>0.19295</v>
+      </c>
+      <c r="Q125" t="n">
+        <v>0.11735</v>
+      </c>
+      <c r="R125" t="n">
+        <v>0.13951</v>
+      </c>
+      <c r="S125" t="n">
+        <v>0.19899</v>
+      </c>
+      <c r="T125" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="U125" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="V125" t="n">
+        <v>0.1123</v>
+      </c>
+      <c r="W125" t="n">
+        <v>-0.03391</v>
+      </c>
+      <c r="X125" t="n">
+        <v>0.12904</v>
+      </c>
+      <c r="Y125" t="n">
+        <v>0.10363</v>
+      </c>
+      <c r="Z125" t="n">
+        <v>0.0857</v>
+      </c>
+      <c r="AA125" t="n">
+        <v>0.02996</v>
+      </c>
+      <c r="AB125" t="n">
+        <v>0.09003</v>
+      </c>
+      <c r="AC125" t="n">
+        <v>0.11466</v>
+      </c>
+      <c r="AD125" t="n">
+        <v>0.17016</v>
+      </c>
+      <c r="AE125" t="n">
+        <v>0.21271</v>
+      </c>
+      <c r="AF125" t="n">
+        <v>0.16232</v>
+      </c>
+      <c r="AG125" t="n">
+        <v>0.19063</v>
+      </c>
+      <c r="AH125" t="n">
+        <v>0.18656</v>
+      </c>
+      <c r="AI125" t="n">
+        <v>0.15295</v>
+      </c>
+      <c r="AJ125" t="n">
+        <v>0.26148</v>
+      </c>
+      <c r="AK125" t="n">
+        <v>0.26967</v>
+      </c>
+      <c r="AL125" t="n">
+        <v>0.29186</v>
+      </c>
+      <c r="AM125" t="n">
+        <v>0.31174</v>
+      </c>
+      <c r="AN125" t="n">
+        <v>0.09562000000000001</v>
+      </c>
+      <c r="AO125" t="n">
+        <v>0.25934</v>
+      </c>
+      <c r="AP125" t="n">
+        <v>-0.04783</v>
+      </c>
+      <c r="AQ125" t="n">
+        <v>0.30408</v>
+      </c>
+      <c r="AR125" t="n">
+        <v>0.31053</v>
+      </c>
+      <c r="AS125" t="n">
+        <v>0.25191</v>
+      </c>
+      <c r="AT125" t="n">
+        <v>0.27086</v>
+      </c>
+      <c r="AU125" t="n">
+        <v>0.13695</v>
+      </c>
+      <c r="AV125" t="n">
+        <v>0.25998</v>
+      </c>
+      <c r="AW125" t="n">
+        <v>0.25952</v>
+      </c>
+      <c r="AX125" t="n">
+        <v>0.2042</v>
+      </c>
+      <c r="AY125" t="n">
+        <v>0.31883</v>
+      </c>
+      <c r="AZ125" t="n">
+        <v>0.29897</v>
+      </c>
+      <c r="BA125" t="n">
+        <v>0.33206</v>
+      </c>
+      <c r="BB125" t="n">
+        <v>0.29198</v>
+      </c>
+      <c r="BC125" t="n">
+        <v>0.32158</v>
+      </c>
+      <c r="BD125" t="n">
+        <v>0.32186</v>
+      </c>
+      <c r="BE125" t="n">
+        <v>0.37168</v>
+      </c>
+      <c r="BF125" t="n">
+        <v>0.38543</v>
+      </c>
+      <c r="BG125" t="n">
+        <v>0.28434</v>
+      </c>
+      <c r="BH125" t="n">
+        <v>0.1881</v>
+      </c>
+      <c r="BI125" t="n">
+        <v>0.21826</v>
+      </c>
+      <c r="BJ125" t="n">
+        <v>0.27866</v>
+      </c>
+      <c r="BK125" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BL125" t="n">
+        <v>0.25841</v>
+      </c>
+      <c r="BM125" t="n">
+        <v>0.20837</v>
+      </c>
+      <c r="BN125" t="n">
+        <v>0.31998</v>
+      </c>
+      <c r="BO125" t="n">
+        <v>0.22622</v>
+      </c>
+      <c r="BP125" t="n">
+        <v>0.18331</v>
+      </c>
+      <c r="BQ125" t="n">
+        <v>0.28498</v>
+      </c>
+      <c r="BR125" t="n">
+        <v>0.29669</v>
+      </c>
+      <c r="BS125" t="n">
+        <v>0.16008</v>
+      </c>
+      <c r="BT125" t="n">
+        <v>0.26409</v>
+      </c>
+      <c r="BU125" t="n">
+        <v>0.13597</v>
+      </c>
+      <c r="BV125" t="n">
+        <v>0.16746</v>
+      </c>
+      <c r="BW125" t="n">
+        <v>0.19698</v>
+      </c>
+      <c r="BX125" t="n">
+        <v>0.19283</v>
+      </c>
+      <c r="BY125" t="n">
+        <v>0.28561</v>
+      </c>
+      <c r="BZ125" t="n">
+        <v>0.09204000000000001</v>
+      </c>
+      <c r="CA125" t="n">
+        <v>0.19974</v>
+      </c>
+      <c r="CB125" t="n">
+        <v>0.14749</v>
+      </c>
+      <c r="CC125" t="n">
+        <v>0.1802</v>
+      </c>
+      <c r="CD125" t="n">
+        <v>0.13615</v>
+      </c>
+      <c r="CE125" t="n">
+        <v>0.20841</v>
+      </c>
+      <c r="CF125" t="n">
+        <v>0.07518000000000001</v>
+      </c>
+      <c r="CG125" t="n">
+        <v>0.19076</v>
+      </c>
+      <c r="CH125" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="CI125" t="n">
+        <v>0.22714</v>
+      </c>
+      <c r="CJ125" t="n">
+        <v>0.20587</v>
+      </c>
+      <c r="CK125" t="n">
+        <v>0.4363</v>
+      </c>
+      <c r="CL125" t="n">
+        <v>0.23768</v>
+      </c>
+      <c r="CM125" t="n">
+        <v>0.3274</v>
+      </c>
+      <c r="CN125" t="n">
+        <v>0.14743</v>
+      </c>
+      <c r="CO125" t="n">
+        <v>0.03624</v>
+      </c>
+      <c r="CP125" t="n">
+        <v>0.22558</v>
+      </c>
+      <c r="CQ125" t="n">
+        <v>-0.02179</v>
+      </c>
+      <c r="CR125" t="n">
+        <v>-0.04645000000000001</v>
+      </c>
+      <c r="CS125" t="n">
+        <v>-0.05</v>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" s="2" t="n">
+        <v>46147</v>
+      </c>
+      <c r="B126" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="C126" t="n">
+        <v>0.67279</v>
+      </c>
+      <c r="D126" t="n">
+        <v>1.36776</v>
+      </c>
+      <c r="E126" t="n">
+        <v>1.08765</v>
+      </c>
+      <c r="F126" t="n">
+        <v>0.59385</v>
+      </c>
+      <c r="G126" t="n">
+        <v>0.6877300000000001</v>
+      </c>
+      <c r="H126" t="n">
+        <v>0.54365</v>
+      </c>
+      <c r="I126" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="J126" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="K126" t="n">
+        <v>0.33188</v>
+      </c>
+      <c r="L126" t="n">
+        <v>0.38414</v>
+      </c>
+      <c r="M126" t="n">
+        <v>0.31892</v>
+      </c>
+      <c r="N126" t="n">
+        <v>0.04361</v>
+      </c>
+      <c r="O126" t="n">
+        <v>0.29449</v>
+      </c>
+      <c r="P126" t="n">
+        <v>0.28584</v>
+      </c>
+      <c r="Q126" t="n">
+        <v>0.05577</v>
+      </c>
+      <c r="R126" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="S126" t="n">
+        <v>0.28478</v>
+      </c>
+      <c r="T126" t="n">
+        <v>0.30902</v>
+      </c>
+      <c r="U126" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="V126" t="n">
+        <v>0.30735</v>
+      </c>
+      <c r="W126" t="n">
+        <v>0.25379</v>
+      </c>
+      <c r="X126" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="Y126" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="Z126" t="n">
+        <v>0.26718</v>
+      </c>
+      <c r="AA126" t="n">
+        <v>0.29247</v>
+      </c>
+      <c r="AB126" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AC126" t="n">
+        <v>0.28463</v>
+      </c>
+      <c r="AD126" t="n">
+        <v>0.27431</v>
+      </c>
+      <c r="AE126" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AF126" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AG126" t="n">
+        <v>0.26974</v>
+      </c>
+      <c r="AH126" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AI126" t="n">
+        <v>0.36673</v>
+      </c>
+      <c r="AJ126" t="n">
+        <v>0.22409</v>
+      </c>
+      <c r="AK126" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AL126" t="n">
+        <v>0.16875</v>
+      </c>
+      <c r="AM126" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AN126" t="n">
+        <v>0.08871</v>
+      </c>
+      <c r="AO126" t="n">
+        <v>0.20704</v>
+      </c>
+      <c r="AP126" t="n">
+        <v>0.16791</v>
+      </c>
+      <c r="AQ126" t="n">
+        <v>0.24704</v>
+      </c>
+      <c r="AR126" t="n">
+        <v>0.20451</v>
+      </c>
+      <c r="AS126" t="n">
+        <v>0.22168</v>
+      </c>
+      <c r="AT126" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AU126" t="n">
+        <v>-0.04338</v>
+      </c>
+      <c r="AV126" t="n">
+        <v>0.23496</v>
+      </c>
+      <c r="AW126" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AX126" t="n">
+        <v>0.25552</v>
+      </c>
+      <c r="AY126" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AZ126" t="n">
+        <v>0.23814</v>
+      </c>
+      <c r="BA126" t="n">
+        <v>0.11018</v>
+      </c>
+      <c r="BB126" t="n">
+        <v>0.20753</v>
+      </c>
+      <c r="BC126" t="n">
+        <v>0.2775</v>
+      </c>
+      <c r="BD126" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BE126" t="n">
+        <v>0.30167</v>
+      </c>
+      <c r="BF126" t="n">
+        <v>0.29885</v>
+      </c>
+      <c r="BG126" t="n">
+        <v>0.26935</v>
+      </c>
+      <c r="BH126" t="n">
+        <v>0.26571</v>
+      </c>
+      <c r="BI126" t="n">
+        <v>0.31419</v>
+      </c>
+      <c r="BJ126" t="n">
+        <v>0.28786</v>
+      </c>
+      <c r="BK126" t="n">
+        <v>0.24627</v>
+      </c>
+      <c r="BL126" t="n">
+        <v>0.25121</v>
+      </c>
+      <c r="BM126" t="n">
+        <v>0.25455</v>
+      </c>
+      <c r="BN126" t="n">
+        <v>0.25711</v>
+      </c>
+      <c r="BO126" t="n">
+        <v>0.26493</v>
+      </c>
+      <c r="BP126" t="n">
+        <v>0.22222</v>
+      </c>
+      <c r="BQ126" t="n">
+        <v>0.19533</v>
+      </c>
+      <c r="BR126" t="n">
+        <v>0.22148</v>
+      </c>
+      <c r="BS126" t="n">
+        <v>0.15031</v>
+      </c>
+      <c r="BT126" t="n">
+        <v>0.15327</v>
+      </c>
+      <c r="BU126" t="n">
+        <v>0.08026999999999999</v>
+      </c>
+      <c r="BV126" t="n">
+        <v>0.07296</v>
+      </c>
+      <c r="BW126" t="n">
+        <v>0.2384</v>
+      </c>
+      <c r="BX126" t="n">
+        <v>0.22893</v>
+      </c>
+      <c r="BY126" t="n">
+        <v>0.2198</v>
+      </c>
+      <c r="BZ126" t="n">
+        <v>0.05119</v>
+      </c>
+      <c r="CA126" t="n">
+        <v>0.22019</v>
+      </c>
+      <c r="CB126" t="n">
+        <v>0.21114</v>
+      </c>
+      <c r="CC126" t="n">
+        <v>-0.00264</v>
+      </c>
+      <c r="CD126" t="n">
+        <v>0.1648</v>
+      </c>
+      <c r="CE126" t="n">
+        <v>0.23148</v>
+      </c>
+      <c r="CF126" t="n">
+        <v>0.21724</v>
+      </c>
+      <c r="CG126" t="n">
+        <v>-0.02139</v>
+      </c>
+      <c r="CH126" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="CI126" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="CJ126" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="CK126" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="CL126" t="n">
+        <v>0.06984</v>
+      </c>
+      <c r="CM126" t="n">
+        <v>0.05490999999999999</v>
+      </c>
+      <c r="CN126" t="n">
+        <v>0.07099999999999999</v>
+      </c>
+      <c r="CO126" t="n">
+        <v>0.08907</v>
+      </c>
+      <c r="CP126" t="n">
+        <v>0.14533</v>
+      </c>
+      <c r="CQ126" t="n">
+        <v>0.01422</v>
+      </c>
+      <c r="CR126" t="n">
+        <v>0.14945</v>
+      </c>
+      <c r="CS126" t="n">
+        <v>0.00453</v>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" s="2" t="n">
+        <v>46148</v>
+      </c>
+      <c r="B127" t="n">
+        <v>0.3183</v>
+      </c>
+      <c r="C127" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="D127" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="E127" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="F127" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="G127" t="n">
+        <v>0.19578</v>
+      </c>
+      <c r="H127" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="I127" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="J127" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="K127" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="L127" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="M127" t="n">
+        <v>-0.04954</v>
+      </c>
+      <c r="N127" t="n">
+        <v>-0.01557</v>
+      </c>
+      <c r="O127" t="n">
+        <v>-0.02095</v>
+      </c>
+      <c r="P127" t="n">
+        <v>0.1863</v>
+      </c>
+      <c r="Q127" t="n">
+        <v>0.18229</v>
+      </c>
+      <c r="R127" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="S127" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="T127" t="n">
+        <v>0.18192</v>
+      </c>
+      <c r="U127" t="n">
+        <v>0.19739</v>
+      </c>
+      <c r="V127" t="n">
+        <v>0.17766</v>
+      </c>
+      <c r="W127" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="X127" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="Y127" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="Z127" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AA127" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AB127" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AC127" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AD127" t="n">
+        <v>-0.03342</v>
+      </c>
+      <c r="AE127" t="n">
+        <v>0.20554</v>
+      </c>
+      <c r="AF127" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AG127" t="n">
+        <v>0.05213</v>
+      </c>
+      <c r="AH127" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AI127" t="n">
+        <v>0.18155</v>
+      </c>
+      <c r="AJ127" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AK127" t="n">
+        <v>0.15889</v>
+      </c>
+      <c r="AL127" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AM127" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AN127" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AO127" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AP127" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AQ127" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AR127" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AS127" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AT127" t="n">
+        <v>0.28685</v>
+      </c>
+      <c r="AU127" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AV127" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AW127" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AX127" t="n">
+        <v>-0.02433</v>
+      </c>
+      <c r="AY127" t="n">
+        <v>-0.00514</v>
+      </c>
+      <c r="AZ127" t="n">
+        <v>0.27204</v>
+      </c>
+      <c r="BA127" t="n">
+        <v>0.01562</v>
+      </c>
+      <c r="BB127" t="n">
+        <v>0.19968</v>
+      </c>
+      <c r="BC127" t="n">
+        <v>-0.02112</v>
+      </c>
+      <c r="BD127" t="n">
+        <v>0.25792</v>
+      </c>
+      <c r="BE127" t="n">
+        <v>0.21985</v>
+      </c>
+      <c r="BF127" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BG127" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BH127" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BI127" t="n">
+        <v>-0.04635</v>
+      </c>
+      <c r="BJ127" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BK127" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BL127" t="n">
+        <v>-0.04806000000000001</v>
+      </c>
+      <c r="BM127" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BN127" t="n">
+        <v>0.15609</v>
+      </c>
+      <c r="BO127" t="n">
+        <v>0.02768</v>
+      </c>
+      <c r="BP127" t="n">
+        <v>0.13623</v>
+      </c>
+      <c r="BQ127" t="n">
+        <v>0.03906</v>
+      </c>
+      <c r="BR127" t="n">
+        <v>0.31832</v>
+      </c>
+      <c r="BS127" t="n">
+        <v>0.08931</v>
+      </c>
+      <c r="BT127" t="n">
+        <v>0.02348</v>
+      </c>
+      <c r="BU127" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BV127" t="n">
+        <v>0.13831</v>
+      </c>
+      <c r="BW127" t="n">
+        <v>0.0256</v>
+      </c>
+      <c r="BX127" t="n">
+        <v>0.14125</v>
+      </c>
+      <c r="BY127" t="n">
+        <v>-0.0311</v>
+      </c>
+      <c r="BZ127" t="n">
+        <v>0.04486</v>
+      </c>
+      <c r="CA127" t="n">
+        <v>-0.03062</v>
+      </c>
+      <c r="CB127" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="CC127" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="CD127" t="n">
+        <v>-0.03573</v>
+      </c>
+      <c r="CE127" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="CF127" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="CG127" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="CH127" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="CI127" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="CJ127" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="CK127" t="n">
+        <v>0.30425</v>
+      </c>
+      <c r="CL127" t="n">
+        <v>0.2681</v>
+      </c>
+      <c r="CM127" t="n">
+        <v>0.25562</v>
+      </c>
+      <c r="CN127" t="n">
+        <v>0.2607</v>
+      </c>
+      <c r="CO127" t="n">
+        <v>0.25426</v>
+      </c>
+      <c r="CP127" t="n">
+        <v>0.01222</v>
+      </c>
+      <c r="CQ127" t="n">
+        <v>0.02109</v>
+      </c>
+      <c r="CR127" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="CS127" t="n">
+        <v>0.03617</v>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" s="2" t="n">
+        <v>46149</v>
+      </c>
+      <c r="B128" t="n">
+        <v>0.10921</v>
+      </c>
+      <c r="C128" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="D128" t="n">
+        <v>0.24927</v>
+      </c>
+      <c r="E128" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="F128" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="G128" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="H128" t="n">
+        <v>0.03838</v>
+      </c>
+      <c r="I128" t="n">
+        <v>0.008919999999999999</v>
+      </c>
+      <c r="J128" t="n">
+        <v>0.01876</v>
+      </c>
+      <c r="K128" t="n">
+        <v>-0.01107</v>
+      </c>
+      <c r="L128" t="n">
+        <v>0.24019</v>
+      </c>
+      <c r="M128" t="n">
+        <v>0.23081</v>
+      </c>
+      <c r="N128" t="n">
+        <v>0.04777</v>
+      </c>
+      <c r="O128" t="n">
+        <v>0.10422</v>
+      </c>
+      <c r="P128" t="n">
+        <v>0.00212</v>
+      </c>
+      <c r="Q128" t="n">
+        <v>0.06264</v>
+      </c>
+      <c r="R128" t="n">
+        <v>-0.00242</v>
+      </c>
+      <c r="S128" t="n">
+        <v>0.09813</v>
+      </c>
+      <c r="T128" t="n">
+        <v>0.10745</v>
+      </c>
+      <c r="U128" t="n">
+        <v>0.09647</v>
+      </c>
+      <c r="V128" t="n">
+        <v>0.11501</v>
+      </c>
+      <c r="W128" t="n">
+        <v>0.12687</v>
+      </c>
+      <c r="X128" t="n">
+        <v>0.11547</v>
+      </c>
+      <c r="Y128" t="n">
+        <v>0.12687</v>
+      </c>
+      <c r="Z128" t="n">
+        <v>0.11902</v>
+      </c>
+      <c r="AA128" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AB128" t="n">
+        <v>0.0236</v>
+      </c>
+      <c r="AC128" t="n">
+        <v>0.01061</v>
+      </c>
+      <c r="AD128" t="n">
+        <v>0.08064</v>
+      </c>
+      <c r="AE128" t="n">
+        <v>0.15868</v>
+      </c>
+      <c r="AF128" t="n">
+        <v>0.11071</v>
+      </c>
+      <c r="AG128" t="n">
+        <v>0.15887</v>
+      </c>
+      <c r="AH128" t="n">
+        <v>0.1732</v>
+      </c>
+      <c r="AI128" t="n">
+        <v>0.15537</v>
+      </c>
+      <c r="AJ128" t="n">
+        <v>0.15853</v>
+      </c>
+      <c r="AK128" t="n">
+        <v>0.21894</v>
+      </c>
+      <c r="AL128" t="n">
+        <v>0.22552</v>
+      </c>
+      <c r="AM128" t="n">
+        <v>0.19509</v>
+      </c>
+      <c r="AN128" t="n">
+        <v>0.31541</v>
+      </c>
+      <c r="AO128" t="n">
+        <v>0.27287</v>
+      </c>
+      <c r="AP128" t="n">
+        <v>0.244</v>
+      </c>
+      <c r="AQ128" t="n">
+        <v>0.23515</v>
+      </c>
+      <c r="AR128" t="n">
+        <v>0.25849</v>
+      </c>
+      <c r="AS128" t="n">
+        <v>0.18245</v>
+      </c>
+      <c r="AT128" t="n">
+        <v>0.14267</v>
+      </c>
+      <c r="AU128" t="n">
+        <v>0.18199</v>
+      </c>
+      <c r="AV128" t="n">
+        <v>0.1784</v>
+      </c>
+      <c r="AW128" t="n">
+        <v>-0.02764</v>
+      </c>
+      <c r="AX128" t="n">
+        <v>0.21686</v>
+      </c>
+      <c r="AY128" t="n">
+        <v>0.30085</v>
+      </c>
+      <c r="AZ128" t="n">
+        <v>0.30084</v>
+      </c>
+      <c r="BA128" t="n">
+        <v>0.31753</v>
+      </c>
+      <c r="BB128" t="n">
+        <v>0.31506</v>
+      </c>
+      <c r="BC128" t="n">
+        <v>0.2805299999999999</v>
+      </c>
+      <c r="BD128" t="n">
+        <v>0.13751</v>
+      </c>
+      <c r="BE128" t="n">
+        <v>0.31289</v>
+      </c>
+      <c r="BF128" t="n">
+        <v>0.26123</v>
+      </c>
+      <c r="BG128" t="n">
+        <v>0.2423</v>
+      </c>
+      <c r="BH128" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BI128" t="n">
+        <v>0.16225</v>
+      </c>
+      <c r="BJ128" t="n">
+        <v>0.08076999999999999</v>
+      </c>
+      <c r="BK128" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BL128" t="n">
+        <v>0.08156000000000001</v>
+      </c>
+      <c r="BM128" t="n">
+        <v>0.11724</v>
+      </c>
+      <c r="BN128" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BO128" t="n">
+        <v>0.16469</v>
+      </c>
+      <c r="BP128" t="n">
+        <v>0.09601000000000001</v>
+      </c>
+      <c r="BQ128" t="n">
+        <v>0.18335</v>
+      </c>
+      <c r="BR128" t="n">
+        <v>0.19644</v>
+      </c>
+      <c r="BS128" t="n">
+        <v>0.11347</v>
+      </c>
+      <c r="BT128" t="n">
+        <v>0.20278</v>
+      </c>
+      <c r="BU128" t="n">
+        <v>0.21149</v>
+      </c>
+      <c r="BV128" t="n">
+        <v>0.22678</v>
+      </c>
+      <c r="BW128" t="n">
+        <v>0.21969</v>
+      </c>
+      <c r="BX128" t="n">
+        <v>0.17115</v>
+      </c>
+      <c r="BY128" t="n">
+        <v>0.14778</v>
+      </c>
+      <c r="BZ128" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="CA128" t="n">
+        <v>0.1901</v>
+      </c>
+      <c r="CB128" t="n">
+        <v>0.41419</v>
+      </c>
+      <c r="CC128" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="CD128" t="n">
+        <v>0.31611</v>
+      </c>
+      <c r="CE128" t="n">
+        <v>0.19184</v>
+      </c>
+      <c r="CF128" t="n">
+        <v>0.18804</v>
+      </c>
+      <c r="CG128" t="n">
+        <v>0.12719</v>
+      </c>
+      <c r="CH128" t="n">
+        <v>0.12607</v>
+      </c>
+      <c r="CI128" t="n">
+        <v>0.0401</v>
+      </c>
+      <c r="CJ128" t="n">
+        <v>0.22063</v>
+      </c>
+      <c r="CK128" t="n">
+        <v>0.20604</v>
+      </c>
+      <c r="CL128" t="n">
+        <v>0.16026</v>
+      </c>
+      <c r="CM128" t="n">
+        <v>0.1347</v>
+      </c>
+      <c r="CN128" t="n">
+        <v>0.1772</v>
+      </c>
+      <c r="CO128" t="n">
+        <v>-0.04977</v>
+      </c>
+      <c r="CP128" t="n">
+        <v>0.04966</v>
+      </c>
+      <c r="CQ128" t="n">
+        <v>0.03822</v>
+      </c>
+      <c r="CR128" t="n">
+        <v>0.13925</v>
+      </c>
+      <c r="CS128" t="n">
+        <v>0.10397</v>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" s="2" t="n">
+        <v>46150</v>
+      </c>
+      <c r="B129" t="n">
+        <v>0.24465</v>
+      </c>
+      <c r="C129" t="n">
+        <v>0.09629</v>
+      </c>
+      <c r="D129" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="E129" t="n">
+        <v>0.23138</v>
+      </c>
+      <c r="F129" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="G129" t="n">
+        <v>0.05899</v>
+      </c>
+      <c r="H129" t="n">
+        <v>0.12616</v>
+      </c>
+      <c r="I129" t="n">
+        <v>-0.01371</v>
+      </c>
+      <c r="J129" t="n">
+        <v>0.04763000000000001</v>
+      </c>
+      <c r="K129" t="n">
+        <v>0.04869</v>
+      </c>
+      <c r="L129" t="n">
+        <v>0.11113</v>
+      </c>
+      <c r="M129" t="n">
+        <v>0.09620999999999999</v>
+      </c>
+      <c r="N129" t="n">
+        <v>0.12148</v>
+      </c>
+      <c r="O129" t="n">
+        <v>0.11611</v>
+      </c>
+      <c r="P129" t="n">
+        <v>0.20763</v>
+      </c>
+      <c r="Q129" t="n">
+        <v>0.09198999999999999</v>
+      </c>
+      <c r="R129" t="n">
+        <v>0.12145</v>
+      </c>
+      <c r="S129" t="n">
+        <v>0.12462</v>
+      </c>
+      <c r="T129" t="n">
+        <v>0.20386</v>
+      </c>
+      <c r="U129" t="n">
+        <v>0.19932</v>
+      </c>
+      <c r="V129" t="n">
+        <v>0.1295</v>
+      </c>
+      <c r="W129" t="n">
+        <v>0.20063</v>
+      </c>
+      <c r="X129" t="n">
+        <v>0.19596</v>
+      </c>
+      <c r="Y129" t="n">
+        <v>0.12506</v>
+      </c>
+      <c r="Z129" t="n">
+        <v>0.12482</v>
+      </c>
+      <c r="AA129" t="n">
+        <v>0.09773999999999999</v>
+      </c>
+      <c r="AB129" t="n">
+        <v>-0.04287</v>
+      </c>
+      <c r="AC129" t="n">
+        <v>0.24074</v>
+      </c>
+      <c r="AD129" t="n">
+        <v>0.04898</v>
+      </c>
+      <c r="AE129" t="n">
+        <v>0.08876000000000001</v>
+      </c>
+      <c r="AF129" t="n">
+        <v>0.20101</v>
+      </c>
+      <c r="AG129" t="n">
+        <v>0.13062</v>
+      </c>
+      <c r="AH129" t="n">
+        <v>0.1098</v>
+      </c>
+      <c r="AI129" t="n">
+        <v>0.23268</v>
+      </c>
+      <c r="AJ129" t="n">
+        <v>0.30233</v>
+      </c>
+      <c r="AK129" t="n">
+        <v>1.00189</v>
+      </c>
+      <c r="AL129" t="n">
+        <v>0.29695</v>
+      </c>
+      <c r="AM129" t="n">
+        <v>0.54743</v>
+      </c>
+      <c r="AN129" t="n">
+        <v>0.24329</v>
+      </c>
+      <c r="AO129" t="n">
+        <v>0.37868</v>
+      </c>
+      <c r="AP129" t="n">
+        <v>0.34987</v>
+      </c>
+      <c r="AQ129" t="n">
+        <v>0.2359</v>
+      </c>
+      <c r="AR129" t="n">
+        <v>0.30808</v>
+      </c>
+      <c r="AS129" t="n">
+        <v>0.34898</v>
+      </c>
+      <c r="AT129" t="n">
+        <v>0.22644</v>
+      </c>
+      <c r="AU129" t="n">
+        <v>0.2909</v>
+      </c>
+      <c r="AV129" t="n">
+        <v>0.23131</v>
+      </c>
+      <c r="AW129" t="n">
+        <v>0.38797</v>
+      </c>
+      <c r="AX129" t="n">
+        <v>0.26784</v>
+      </c>
+      <c r="AY129" t="n">
+        <v>0.27136</v>
+      </c>
+      <c r="AZ129" t="n">
+        <v>0.1225</v>
+      </c>
+      <c r="BA129" t="n">
+        <v>0.20421</v>
+      </c>
+      <c r="BB129" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BC129" t="n">
+        <v>0.30652</v>
+      </c>
+      <c r="BD129" t="n">
+        <v>0.27045</v>
+      </c>
+      <c r="BE129" t="n">
+        <v>0.47704</v>
+      </c>
+      <c r="BF129" t="n">
+        <v>0.25807</v>
+      </c>
+      <c r="BG129" t="n">
+        <v>0.23196</v>
+      </c>
+      <c r="BH129" t="n">
+        <v>0.2583</v>
+      </c>
+      <c r="BI129" t="n">
+        <v>0.24528</v>
+      </c>
+      <c r="BJ129" t="n">
+        <v>0.20909</v>
+      </c>
+      <c r="BK129" t="n">
+        <v>0.366</v>
+      </c>
+      <c r="BL129" t="n">
+        <v>0.259</v>
+      </c>
+      <c r="BM129" t="n">
+        <v>0.18004</v>
+      </c>
+      <c r="BN129" t="n">
+        <v>0.25935</v>
+      </c>
+      <c r="BO129" t="n">
+        <v>0.02006</v>
+      </c>
+      <c r="BP129" t="n">
+        <v>0.15321</v>
+      </c>
+      <c r="BQ129" t="n">
+        <v>0.22996</v>
+      </c>
+      <c r="BR129" t="n">
+        <v>0.24689</v>
+      </c>
+      <c r="BS129" t="n">
+        <v>0.1971</v>
+      </c>
+      <c r="BT129" t="n">
+        <v>0.20356</v>
+      </c>
+      <c r="BU129" t="n">
+        <v>0.30297</v>
+      </c>
+      <c r="BV129" t="n">
+        <v>0.35094</v>
+      </c>
+      <c r="BW129" t="n">
+        <v>0.23484</v>
+      </c>
+      <c r="BX129" t="n">
+        <v>0.47439</v>
+      </c>
+      <c r="BY129" t="n">
+        <v>0.33824</v>
+      </c>
+      <c r="BZ129" t="n">
+        <v>0.25475</v>
+      </c>
+      <c r="CA129" t="n">
+        <v>0.32933</v>
+      </c>
+      <c r="CB129" t="n">
+        <v>0.31054</v>
+      </c>
+      <c r="CC129" t="n">
+        <v>0.57921</v>
+      </c>
+      <c r="CD129" t="n">
+        <v>0.24806</v>
+      </c>
+      <c r="CE129" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="CF129" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="CG129" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="CH129" t="n">
+        <v>0.23215</v>
+      </c>
+      <c r="CI129" t="n">
+        <v>0.36754</v>
+      </c>
+      <c r="CJ129" t="n">
+        <v>0.11242</v>
+      </c>
+      <c r="CK129" t="n">
+        <v>0.15163</v>
+      </c>
+      <c r="CL129" t="n">
+        <v>0.36163</v>
+      </c>
+      <c r="CM129" t="n">
+        <v>0.17583</v>
+      </c>
+      <c r="CN129" t="n">
+        <v>0.25968</v>
+      </c>
+      <c r="CO129" t="n">
+        <v>0.1494</v>
+      </c>
+      <c r="CP129" t="n">
+        <v>0.02894</v>
+      </c>
+      <c r="CQ129" t="n">
+        <v>0.04297</v>
+      </c>
+      <c r="CR129" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="CS129" t="n">
+        <v>-0.05</v>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" s="2" t="n">
+        <v>46151</v>
+      </c>
+      <c r="B130" t="n">
+        <v>0.32005</v>
+      </c>
+      <c r="C130" t="n">
+        <v>0.01345</v>
+      </c>
+      <c r="D130" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="E130" t="n">
+        <v>0.27063</v>
+      </c>
+      <c r="F130" t="n">
+        <v>0.04602000000000001</v>
+      </c>
+      <c r="G130" t="n">
+        <v>0.07398</v>
+      </c>
+      <c r="H130" t="n">
+        <v>0.02834</v>
+      </c>
+      <c r="I130" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="J130" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="K130" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="L130" t="n">
+        <v>0.05511</v>
+      </c>
+      <c r="M130" t="n">
+        <v>0.03793999999999999</v>
+      </c>
+      <c r="N130" t="n">
+        <v>0.06993000000000001</v>
+      </c>
+      <c r="O130" t="n">
+        <v>0.06734999999999999</v>
+      </c>
+      <c r="P130" t="n">
+        <v>0.07140000000000001</v>
+      </c>
+      <c r="Q130" t="n">
+        <v>0.08070999999999999</v>
+      </c>
+      <c r="R130" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="S130" t="n">
+        <v>0.18572</v>
+      </c>
+      <c r="T130" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="U130" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="V130" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="W130" t="n">
+        <v>0.1809</v>
+      </c>
+      <c r="X130" t="n">
+        <v>0.18407</v>
+      </c>
+      <c r="Y130" t="n">
+        <v>0.02729</v>
+      </c>
+      <c r="Z130" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AA130" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AB130" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AC130" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AD130" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AE130" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AF130" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AG130" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AH130" t="n">
+        <v>0.10136</v>
+      </c>
+      <c r="AI130" t="n">
+        <v>0.21674</v>
+      </c>
+      <c r="AJ130" t="n">
+        <v>0.24244</v>
+      </c>
+      <c r="AK130" t="n">
+        <v>0.24486</v>
+      </c>
+      <c r="AL130" t="n">
+        <v>0.19713</v>
+      </c>
+      <c r="AM130" t="n">
+        <v>0.20889</v>
+      </c>
+      <c r="AN130" t="n">
+        <v>-0.00091</v>
+      </c>
+      <c r="AO130" t="n">
+        <v>0.20881</v>
+      </c>
+      <c r="AP130" t="n">
+        <v>0.24459</v>
+      </c>
+      <c r="AQ130" t="n">
+        <v>0.20917</v>
+      </c>
+      <c r="AR130" t="n">
+        <v>0.13982</v>
+      </c>
+      <c r="AS130" t="n">
+        <v>0.08718000000000001</v>
+      </c>
+      <c r="AT130" t="n">
+        <v>0.1099</v>
+      </c>
+      <c r="AU130" t="n">
+        <v>0.113</v>
+      </c>
+      <c r="AV130" t="n">
+        <v>0.17647</v>
+      </c>
+      <c r="AW130" t="n">
+        <v>0.12837</v>
+      </c>
+      <c r="AX130" t="n">
+        <v>0.14298</v>
+      </c>
+      <c r="AY130" t="n">
+        <v>0.12967</v>
+      </c>
+      <c r="AZ130" t="n">
+        <v>0.20067</v>
+      </c>
+      <c r="BA130" t="n">
+        <v>0.14788</v>
+      </c>
+      <c r="BB130" t="n">
+        <v>0.18497</v>
+      </c>
+      <c r="BC130" t="n">
+        <v>0.18794</v>
+      </c>
+      <c r="BD130" t="n">
+        <v>0.19316</v>
+      </c>
+      <c r="BE130" t="n">
+        <v>0.12461</v>
+      </c>
+      <c r="BF130" t="n">
+        <v>0.11494</v>
+      </c>
+      <c r="BG130" t="n">
+        <v>0.12108</v>
+      </c>
+      <c r="BH130" t="n">
+        <v>0.07201</v>
+      </c>
+      <c r="BI130" t="n">
+        <v>0.12131</v>
+      </c>
+      <c r="BJ130" t="n">
+        <v>0.14099</v>
+      </c>
+      <c r="BK130" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BL130" t="n">
+        <v>0.08828</v>
+      </c>
+      <c r="BM130" t="n">
+        <v>0.21006</v>
+      </c>
+      <c r="BN130" t="n">
+        <v>0.18674</v>
+      </c>
+      <c r="BO130" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BP130" t="n">
+        <v>0.06252000000000001</v>
+      </c>
+      <c r="BQ130" t="n">
+        <v>0.12622</v>
+      </c>
+      <c r="BR130" t="n">
+        <v>0.14327</v>
+      </c>
+      <c r="BS130" t="n">
+        <v>0.21624</v>
+      </c>
+      <c r="BT130" t="n">
+        <v>0.18017</v>
+      </c>
+      <c r="BU130" t="n">
+        <v>0.134</v>
+      </c>
+      <c r="BV130" t="n">
+        <v>0.11344</v>
+      </c>
+      <c r="BW130" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BX130" t="n">
+        <v>0.08817</v>
+      </c>
+      <c r="BY130" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BZ130" t="n">
+        <v>0.20623</v>
+      </c>
+      <c r="CA130" t="n">
+        <v>-0.02916</v>
+      </c>
+      <c r="CB130" t="n">
+        <v>0.22774</v>
+      </c>
+      <c r="CC130" t="n">
+        <v>0.21965</v>
+      </c>
+      <c r="CD130" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="CE130" t="n">
+        <v>0.22084</v>
+      </c>
+      <c r="CF130" t="n">
+        <v>-0.02542</v>
+      </c>
+      <c r="CG130" t="n">
+        <v>0.22109</v>
+      </c>
+      <c r="CH130" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="CI130" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="CJ130" t="n">
+        <v>0.2317</v>
+      </c>
+      <c r="CK130" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="CL130" t="n">
+        <v>0.21566</v>
+      </c>
+      <c r="CM130" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="CN130" t="n">
+        <v>0.22852</v>
+      </c>
+      <c r="CO130" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="CP130" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="CQ130" t="n">
+        <v>0.20937</v>
+      </c>
+      <c r="CR130" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="CS130" t="n">
+        <v>0.20897</v>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" s="2" t="n">
+        <v>46152</v>
+      </c>
+      <c r="B131" t="n">
+        <v>0.11819</v>
+      </c>
+      <c r="C131" t="n">
+        <v>0.20963</v>
+      </c>
+      <c r="D131" t="n">
+        <v>0.20863</v>
+      </c>
+      <c r="E131" t="n">
+        <v>0.20967</v>
+      </c>
+      <c r="F131" t="n">
+        <v>0.2106</v>
+      </c>
+      <c r="G131" t="n">
+        <v>0.21009</v>
+      </c>
+      <c r="H131" t="n">
+        <v>0.20929</v>
+      </c>
+      <c r="I131" t="n">
+        <v>0.02644</v>
+      </c>
+      <c r="J131" t="n">
+        <v>0.20863</v>
+      </c>
+      <c r="K131" t="n">
+        <v>0.20549</v>
+      </c>
+      <c r="L131" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="M131" t="n">
+        <v>0.20627</v>
+      </c>
+      <c r="N131" t="n">
+        <v>0.06850000000000001</v>
+      </c>
+      <c r="O131" t="n">
+        <v>0.04865</v>
+      </c>
+      <c r="P131" t="n">
+        <v>0.03911</v>
+      </c>
+      <c r="Q131" t="n">
+        <v>0.19882</v>
+      </c>
+      <c r="R131" t="n">
+        <v>0.19929</v>
+      </c>
+      <c r="S131" t="n">
+        <v>0.08565</v>
+      </c>
+      <c r="T131" t="n">
+        <v>-0.03561</v>
+      </c>
+      <c r="U131" t="n">
+        <v>0.18363</v>
+      </c>
+      <c r="V131" t="n">
+        <v>0.07815999999999999</v>
+      </c>
+      <c r="W131" t="n">
+        <v>0.19883</v>
+      </c>
+      <c r="X131" t="n">
+        <v>0.03985</v>
+      </c>
+      <c r="Y131" t="n">
+        <v>0.09520999999999999</v>
+      </c>
+      <c r="Z131" t="n">
+        <v>0.02654</v>
+      </c>
+      <c r="AA131" t="n">
+        <v>0.20429</v>
+      </c>
+      <c r="AB131" t="n">
+        <v>0.09270999999999999</v>
+      </c>
+      <c r="AC131" t="n">
+        <v>0.06863</v>
+      </c>
+      <c r="AD131" t="n">
+        <v>0.0663</v>
+      </c>
+      <c r="AE131" t="n">
+        <v>0.19556</v>
+      </c>
+      <c r="AF131" t="n">
+        <v>0.05931</v>
+      </c>
+      <c r="AG131" t="n">
+        <v>0.07346999999999999</v>
+      </c>
+      <c r="AH131" t="n">
+        <v>0.04523</v>
+      </c>
+      <c r="AI131" t="n">
+        <v>0.11664</v>
+      </c>
+      <c r="AJ131" t="n">
+        <v>0.06023</v>
+      </c>
+      <c r="AK131" t="n">
+        <v>0.09229999999999999</v>
+      </c>
+      <c r="AL131" t="n">
+        <v>0.12881</v>
+      </c>
+      <c r="AM131" t="n">
+        <v>0.16148</v>
+      </c>
+      <c r="AN131" t="n">
+        <v>0.19263</v>
+      </c>
+      <c r="AO131" t="n">
+        <v>0.22248</v>
+      </c>
+      <c r="AP131" t="n">
+        <v>0.28412</v>
+      </c>
+      <c r="AQ131" t="n">
+        <v>0.23666</v>
+      </c>
+      <c r="AR131" t="n">
+        <v>0.25362</v>
+      </c>
+      <c r="AS131" t="n">
+        <v>0.26184</v>
+      </c>
+      <c r="AT131" t="n">
+        <v>0.28171</v>
+      </c>
+      <c r="AU131" t="n">
+        <v>0.22235</v>
+      </c>
+      <c r="AV131" t="n">
+        <v>0.22772</v>
+      </c>
+      <c r="AW131" t="n">
+        <v>0.32934</v>
+      </c>
+      <c r="AX131" t="n">
+        <v>0.31826</v>
+      </c>
+      <c r="AY131" t="n">
+        <v>0.37044</v>
+      </c>
+      <c r="AZ131" t="n">
+        <v>0.32501</v>
+      </c>
+      <c r="BA131" t="n">
+        <v>0.31134</v>
+      </c>
+      <c r="BB131" t="n">
+        <v>0.14158</v>
+      </c>
+      <c r="BC131" t="n">
+        <v>0.24586</v>
+      </c>
+      <c r="BD131" t="n">
+        <v>0.28487</v>
+      </c>
+      <c r="BE131" t="n">
+        <v>0.2629</v>
+      </c>
+      <c r="BF131" t="n">
+        <v>0.26644</v>
+      </c>
+      <c r="BG131" t="n">
+        <v>0.2815</v>
+      </c>
+      <c r="BH131" t="n">
+        <v>0.27493</v>
+      </c>
+      <c r="BI131" t="n">
+        <v>0.23775</v>
+      </c>
+      <c r="BJ131" t="n">
+        <v>0.22359</v>
+      </c>
+      <c r="BK131" t="n">
+        <v>0.16535</v>
+      </c>
+      <c r="BL131" t="n">
+        <v>0.25516</v>
+      </c>
+      <c r="BM131" t="n">
+        <v>0.22964</v>
+      </c>
+      <c r="BN131" t="n">
+        <v>0.18028</v>
+      </c>
+      <c r="BO131" t="n">
+        <v>0.19319</v>
+      </c>
+      <c r="BP131" t="n">
+        <v>0.18852</v>
+      </c>
+      <c r="BQ131" t="n">
+        <v>0.21015</v>
+      </c>
+      <c r="BR131" t="n">
+        <v>0.21888</v>
+      </c>
+      <c r="BS131" t="n">
+        <v>0.2293</v>
+      </c>
+      <c r="BT131" t="n">
+        <v>0.2092</v>
+      </c>
+      <c r="BU131" t="n">
+        <v>0.15602</v>
+      </c>
+      <c r="BV131" t="n">
+        <v>0.21173</v>
+      </c>
+      <c r="BW131" t="n">
+        <v>0.15461</v>
+      </c>
+      <c r="BX131" t="n">
+        <v>0.21802</v>
+      </c>
+      <c r="BY131" t="n">
+        <v>0.2233</v>
+      </c>
+      <c r="BZ131" t="n">
+        <v>0.20796</v>
+      </c>
+      <c r="CA131" t="n">
+        <v>0.12527</v>
+      </c>
+      <c r="CB131" t="n">
+        <v>0.02975</v>
+      </c>
+      <c r="CC131" t="n">
+        <v>0.08957</v>
+      </c>
+      <c r="CD131" t="n">
+        <v>0.10243</v>
+      </c>
+      <c r="CE131" t="n">
+        <v>-0.03539</v>
+      </c>
+      <c r="CF131" t="n">
+        <v>0.28414</v>
+      </c>
+      <c r="CG131" t="n">
+        <v>0.10463</v>
+      </c>
+      <c r="CH131" t="n">
+        <v>0.23504</v>
+      </c>
+      <c r="CI131" t="n">
+        <v>0.5142100000000001</v>
+      </c>
+      <c r="CJ131" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="CK131" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="CL131" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="CM131" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="CN131" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="CO131" t="n">
+        <v>0.20961</v>
+      </c>
+      <c r="CP131" t="n">
+        <v>0.21555</v>
+      </c>
+      <c r="CQ131" t="n">
+        <v>0.21837</v>
+      </c>
+      <c r="CR131" t="n">
+        <v>0.1988</v>
+      </c>
+      <c r="CS131" t="n">
+        <v>0.11992</v>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" s="2" t="n">
+        <v>46154</v>
+      </c>
+      <c r="B132" t="n">
+        <v>0.32192</v>
+      </c>
+      <c r="C132" t="n">
+        <v>0.27052</v>
+      </c>
+      <c r="D132" t="n">
+        <v>0.23567</v>
+      </c>
+      <c r="E132" t="n">
+        <v>0.1452</v>
+      </c>
+      <c r="F132" t="n">
+        <v>0.22143</v>
+      </c>
+      <c r="G132" t="n">
+        <v>0.21858</v>
+      </c>
+      <c r="H132" t="n">
+        <v>0.21824</v>
+      </c>
+      <c r="I132" t="n">
+        <v>0.22141</v>
+      </c>
+      <c r="J132" t="n">
+        <v>0.21749</v>
+      </c>
+      <c r="K132" t="n">
+        <v>0.14844</v>
+      </c>
+      <c r="L132" t="n">
+        <v>0.21837</v>
+      </c>
+      <c r="M132" t="n">
+        <v>0.21222</v>
+      </c>
+      <c r="N132" t="n">
+        <v>0.21937</v>
+      </c>
+      <c r="O132" t="n">
+        <v>0.13467</v>
+      </c>
+      <c r="P132" t="n">
+        <v>0.21551</v>
+      </c>
+      <c r="Q132" t="n">
+        <v>0.21147</v>
+      </c>
+      <c r="R132" t="n">
+        <v>0.13379</v>
+      </c>
+      <c r="S132" t="n">
+        <v>0.21887</v>
+      </c>
+      <c r="T132" t="n">
+        <v>0.21919</v>
+      </c>
+      <c r="U132" t="n">
+        <v>0.20694</v>
+      </c>
+      <c r="V132" t="n">
+        <v>-0.0368</v>
+      </c>
+      <c r="W132" t="n">
+        <v>0.21816</v>
+      </c>
+      <c r="X132" t="n">
+        <v>0.2159</v>
+      </c>
+      <c r="Y132" t="n">
+        <v>0.21946</v>
+      </c>
+      <c r="Z132" t="n">
+        <v>0.21946</v>
+      </c>
+      <c r="AA132" t="n">
+        <v>0.04875</v>
+      </c>
+      <c r="AB132" t="n">
+        <v>0.22527</v>
+      </c>
+      <c r="AC132" t="n">
+        <v>0.23927</v>
+      </c>
+      <c r="AD132" t="n">
+        <v>0.21596</v>
+      </c>
+      <c r="AE132" t="n">
+        <v>0.21587</v>
+      </c>
+      <c r="AF132" t="n">
+        <v>0.21057</v>
+      </c>
+      <c r="AG132" t="n">
+        <v>0.21126</v>
+      </c>
+      <c r="AH132" t="n">
+        <v>0.2173</v>
+      </c>
+      <c r="AI132" t="n">
+        <v>0.20221</v>
+      </c>
+      <c r="AJ132" t="n">
+        <v>0.22706</v>
+      </c>
+      <c r="AK132" t="n">
+        <v>0.24467</v>
+      </c>
+      <c r="AL132" t="n">
+        <v>0.18612</v>
+      </c>
+      <c r="AM132" t="n">
+        <v>0.05773</v>
+      </c>
+      <c r="AN132" t="n">
+        <v>0.25038</v>
+      </c>
+      <c r="AO132" t="n">
+        <v>0.03399</v>
+      </c>
+      <c r="AP132" t="n">
+        <v>0.31061</v>
+      </c>
+      <c r="AQ132" t="n">
+        <v>0.28363</v>
+      </c>
+      <c r="AR132" t="n">
+        <v>-0.00088</v>
+      </c>
+      <c r="AS132" t="n">
+        <v>-0.0005600000000000001</v>
+      </c>
+      <c r="AT132" t="n">
+        <v>0.27787</v>
+      </c>
+      <c r="AU132" t="n">
+        <v>0.29288</v>
+      </c>
+      <c r="AV132" t="n">
+        <v>0.29553</v>
+      </c>
+      <c r="AW132" t="n">
+        <v>0.20385</v>
+      </c>
+      <c r="AX132" t="n">
+        <v>0.04797999999999999</v>
+      </c>
+      <c r="AY132" t="n">
+        <v>0.15121</v>
+      </c>
+      <c r="AZ132" t="n">
+        <v>0.21342</v>
+      </c>
+      <c r="BA132" t="n">
+        <v>0.20005</v>
+      </c>
+      <c r="BB132" t="n">
+        <v>0.27135</v>
+      </c>
+      <c r="BC132" t="n">
+        <v>0.24978</v>
+      </c>
+      <c r="BD132" t="n">
+        <v>0.28966</v>
+      </c>
+      <c r="BE132" t="n">
+        <v>0.25841</v>
+      </c>
+      <c r="BF132" t="n">
+        <v>0.17013</v>
+      </c>
+      <c r="BG132" t="n">
+        <v>0.26201</v>
+      </c>
+      <c r="BH132" t="n">
+        <v>0.24009</v>
+      </c>
+      <c r="BI132" t="n">
+        <v>0.20119</v>
+      </c>
+      <c r="BJ132" t="n">
+        <v>0.18492</v>
+      </c>
+      <c r="BK132" t="n">
+        <v>0.18161</v>
+      </c>
+      <c r="BL132" t="n">
+        <v>0.17921</v>
+      </c>
+      <c r="BM132" t="n">
+        <v>0.08935</v>
+      </c>
+      <c r="BN132" t="n">
+        <v>0.21825</v>
+      </c>
+      <c r="BO132" t="n">
+        <v>0.26454</v>
+      </c>
+      <c r="BP132" t="n">
+        <v>0.35715</v>
+      </c>
+      <c r="BQ132" t="n">
+        <v>0.26751</v>
+      </c>
+      <c r="BR132" t="n">
+        <v>0.33374</v>
+      </c>
+      <c r="BS132" t="n">
+        <v>0.25877</v>
+      </c>
+      <c r="BT132" t="n">
+        <v>0.23218</v>
+      </c>
+      <c r="BU132" t="n">
+        <v>0.01289</v>
+      </c>
+      <c r="BV132" t="n">
+        <v>0.3211</v>
+      </c>
+      <c r="BW132" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BX132" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BY132" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BZ132" t="n">
+        <v>0.34507</v>
+      </c>
+      <c r="CA132" t="n">
+        <v>0.53432</v>
+      </c>
+      <c r="CB132" t="n">
+        <v>0.49206</v>
+      </c>
+      <c r="CC132" t="n">
+        <v>0.5239400000000001</v>
+      </c>
+      <c r="CD132" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="CE132" t="n">
+        <v>0.69798</v>
+      </c>
+      <c r="CF132" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="CG132" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="CH132" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="CI132" t="n">
+        <v>0.37869</v>
+      </c>
+      <c r="CJ132" t="n">
+        <v>0.29071</v>
+      </c>
+      <c r="CK132" t="n">
+        <v>0.30068</v>
+      </c>
+      <c r="CL132" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="CM132" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="CN132" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="CO132" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="CP132" t="n">
+        <v>0.10689</v>
+      </c>
+      <c r="CQ132" t="n">
+        <v>0.236</v>
+      </c>
+      <c r="CR132" t="n">
+        <v>0.13171</v>
+      </c>
+      <c r="CS132" t="n">
+        <v>0.14651</v>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" s="2" t="n">
+        <v>46156</v>
+      </c>
+      <c r="B133" t="n">
+        <v>0.34564</v>
+      </c>
+      <c r="C133" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="D133" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="E133" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="F133" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="G133" t="n">
+        <v>-0.03338</v>
+      </c>
+      <c r="H133" t="n">
+        <v>-0.04195</v>
+      </c>
+      <c r="I133" t="n">
+        <v>0.01649</v>
+      </c>
+      <c r="J133" t="n">
+        <v>-0.02801</v>
+      </c>
+      <c r="K133" t="n">
+        <v>0.0032</v>
+      </c>
+      <c r="L133" t="n">
+        <v>-0.03604</v>
+      </c>
+      <c r="M133" t="n">
+        <v>0.03572</v>
+      </c>
+      <c r="N133" t="n">
+        <v>0.25569</v>
+      </c>
+      <c r="O133" t="n">
+        <v>0.05299</v>
+      </c>
+      <c r="P133" t="n">
+        <v>0.05485</v>
+      </c>
+      <c r="Q133" t="n">
+        <v>0.08341</v>
+      </c>
+      <c r="R133" t="n">
+        <v>0.24906</v>
+      </c>
+      <c r="S133" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="T133" t="n">
+        <v>0.02154</v>
+      </c>
+      <c r="U133" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="V133" t="n">
+        <v>0.01261</v>
+      </c>
+      <c r="W133" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="X133" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="Y133" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="Z133" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AA133" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AB133" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AC133" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AD133" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AE133" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AF133" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AG133" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AH133" t="n">
+        <v>0.31785</v>
+      </c>
+      <c r="AI133" t="n">
+        <v>0.25289</v>
+      </c>
+      <c r="AJ133" t="n">
+        <v>0.27944</v>
+      </c>
+      <c r="AK133" t="n">
+        <v>0.29982</v>
+      </c>
+      <c r="AL133" t="n">
+        <v>0.33634</v>
+      </c>
+      <c r="AM133" t="n">
+        <v>0.35479</v>
+      </c>
+      <c r="AN133" t="n">
+        <v>0.4176</v>
+      </c>
+      <c r="AO133" t="n">
+        <v>0.29558</v>
+      </c>
+      <c r="AP133" t="n">
+        <v>0.08597</v>
+      </c>
+      <c r="AQ133" t="n">
+        <v>0.21241</v>
+      </c>
+      <c r="AR133" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AS133" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AT133" t="n">
+        <v>0.05429999999999999</v>
+      </c>
+      <c r="AU133" t="n">
+        <v>0.28588</v>
+      </c>
+      <c r="AV133" t="n">
+        <v>0.23473</v>
+      </c>
+      <c r="AW133" t="n">
+        <v>0.23157</v>
+      </c>
+      <c r="AX133" t="n">
+        <v>0.30087</v>
+      </c>
+      <c r="AY133" t="n">
+        <v>0.33739</v>
+      </c>
+      <c r="AZ133" t="n">
+        <v>0.32848</v>
+      </c>
+      <c r="BA133" t="n">
+        <v>0.40696</v>
+      </c>
+      <c r="BB133" t="n">
+        <v>0.65813</v>
+      </c>
+      <c r="BC133" t="n">
+        <v>0.37956</v>
+      </c>
+      <c r="BD133" t="n">
+        <v>0.72246</v>
+      </c>
+      <c r="BE133" t="n">
+        <v>0.32154</v>
+      </c>
+      <c r="BF133" t="n">
+        <v>-0.03718</v>
+      </c>
+      <c r="BG133" t="n">
+        <v>0.19913</v>
+      </c>
+      <c r="BH133" t="n">
+        <v>0.23519</v>
+      </c>
+      <c r="BI133" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BJ133" t="n">
+        <v>0.3399</v>
+      </c>
+      <c r="BK133" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BL133" t="n">
+        <v>0.15102</v>
+      </c>
+      <c r="BM133" t="n">
+        <v>0.2095</v>
+      </c>
+      <c r="BN133" t="n">
+        <v>0.20794</v>
+      </c>
+      <c r="BO133" t="n">
+        <v>0.13921</v>
+      </c>
+      <c r="BP133" t="n">
+        <v>0.22178</v>
+      </c>
+      <c r="BQ133" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BR133" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BS133" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BT133" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BU133" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BV133" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BW133" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BX133" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BY133" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BZ133" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="CA133" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="CB133" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="CC133" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="CD133" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="CE133" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="CF133" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="CG133" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="CH133" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="CI133" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="CJ133" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="CK133" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="CL133" t="n">
+        <v>0.62895</v>
+      </c>
+      <c r="CM133" t="n">
+        <v>0.48303</v>
+      </c>
+      <c r="CN133" t="n">
+        <v>0.53335</v>
+      </c>
+      <c r="CO133" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="CP133" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="CQ133" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="CR133" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="CS133" t="n">
+        <v>-0.05</v>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" s="2" t="n">
+        <v>46157</v>
+      </c>
+      <c r="B134" t="n">
+        <v>-0.0262</v>
+      </c>
+      <c r="C134" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="D134" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="E134" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="F134" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="G134" t="n">
+        <v>0.29542</v>
+      </c>
+      <c r="H134" t="n">
+        <v>0.28537</v>
+      </c>
+      <c r="I134" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="J134" t="n">
+        <v>0.2770899999999999</v>
+      </c>
+      <c r="K134" t="n">
+        <v>-0.00277</v>
+      </c>
+      <c r="L134" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="M134" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="N134" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="O134" t="n">
+        <v>0.00583</v>
+      </c>
+      <c r="P134" t="n">
+        <v>0.02216</v>
+      </c>
+      <c r="Q134" t="n">
+        <v>0.07912999999999999</v>
+      </c>
+      <c r="R134" t="n">
+        <v>0.05464</v>
+      </c>
+      <c r="S134" t="n">
+        <v>0.22117</v>
+      </c>
+      <c r="T134" t="n">
+        <v>0.21797</v>
+      </c>
+      <c r="U134" t="n">
+        <v>0.22694</v>
+      </c>
+      <c r="V134" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="W134" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="X134" t="n">
+        <v>0.00417</v>
+      </c>
+      <c r="Y134" t="n">
+        <v>0.22083</v>
+      </c>
+      <c r="Z134" t="n">
+        <v>0.22694</v>
+      </c>
+      <c r="AA134" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AB134" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AC134" t="n">
+        <v>0.2405</v>
+      </c>
+      <c r="AD134" t="n">
+        <v>0.01717</v>
+      </c>
+      <c r="AE134" t="n">
+        <v>0.22236</v>
+      </c>
+      <c r="AF134" t="n">
+        <v>0.21613</v>
+      </c>
+      <c r="AG134" t="n">
+        <v>0.24048</v>
+      </c>
+      <c r="AH134" t="n">
+        <v>0.23426</v>
+      </c>
+      <c r="AI134" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AJ134" t="n">
+        <v>0.26274</v>
+      </c>
+      <c r="AK134" t="n">
+        <v>0.26052</v>
+      </c>
+      <c r="AL134" t="n">
+        <v>0.05596</v>
+      </c>
+      <c r="AM134" t="n">
+        <v>0.2477</v>
+      </c>
+      <c r="AN134" t="n">
+        <v>0.35166</v>
+      </c>
+      <c r="AO134" t="n">
+        <v>0.16054</v>
+      </c>
+      <c r="AP134" t="n">
+        <v>0.22913</v>
+      </c>
+      <c r="AQ134" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AR134" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AS134" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AT134" t="n">
+        <v>0.08379</v>
+      </c>
+      <c r="AU134" t="n">
+        <v>0.24248</v>
+      </c>
+      <c r="AV134" t="n">
+        <v>0.29208</v>
+      </c>
+      <c r="AW134" t="n">
+        <v>-0.02609</v>
+      </c>
+      <c r="AX134" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AY134" t="n">
+        <v>0.37498</v>
+      </c>
+      <c r="AZ134" t="n">
+        <v>0.36437</v>
+      </c>
+      <c r="BA134" t="n">
+        <v>0.22878</v>
+      </c>
+      <c r="BB134" t="n">
+        <v>0.37654</v>
+      </c>
+      <c r="BC134" t="n">
+        <v>0.0428</v>
+      </c>
+      <c r="BD134" t="n">
+        <v>0.41339</v>
+      </c>
+      <c r="BE134" t="n">
+        <v>0.14517</v>
+      </c>
+      <c r="BF134" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BG134" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BH134" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BI134" t="n">
+        <v>-0.04563</v>
+      </c>
+      <c r="BJ134" t="n">
+        <v>-0.04183</v>
+      </c>
+      <c r="BK134" t="n">
+        <v>0.08617</v>
+      </c>
+      <c r="BL134" t="n">
+        <v>0.32382</v>
+      </c>
+      <c r="BM134" t="n">
+        <v>0.18252</v>
+      </c>
+      <c r="BN134" t="n">
+        <v>0.18452</v>
+      </c>
+      <c r="BO134" t="n">
+        <v>0.21966</v>
+      </c>
+      <c r="BP134" t="n">
+        <v>0.20436</v>
+      </c>
+      <c r="BQ134" t="n">
+        <v>0.07098</v>
+      </c>
+      <c r="BR134" t="n">
+        <v>0.11275</v>
+      </c>
+      <c r="BS134" t="n">
+        <v>0.04329</v>
+      </c>
+      <c r="BT134" t="n">
+        <v>0.25302</v>
+      </c>
+      <c r="BU134" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BV134" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BW134" t="n">
+        <v>0.30105</v>
+      </c>
+      <c r="BX134" t="n">
+        <v>0.27846</v>
+      </c>
+      <c r="BY134" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BZ134" t="n">
+        <v>0.26903</v>
+      </c>
+      <c r="CA134" t="n">
+        <v>0.05834</v>
+      </c>
+      <c r="CB134" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="CC134" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="CD134" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="CE134" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="CF134" t="n">
+        <v>-0.03434</v>
+      </c>
+      <c r="CG134" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="CH134" t="n">
+        <v>0.2394</v>
+      </c>
+      <c r="CI134" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="CJ134" t="n">
+        <v>0.22126</v>
+      </c>
+      <c r="CK134" t="n">
+        <v>-0.01012</v>
+      </c>
+      <c r="CL134" t="n">
+        <v>0.22273</v>
+      </c>
+      <c r="CM134" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="CN134" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="CO134" t="n">
+        <v>0.14103</v>
+      </c>
+      <c r="CP134" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="CQ134" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="CR134" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="CS134" t="n">
+        <v>-0.05</v>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" s="2" t="n">
+        <v>46158</v>
+      </c>
+      <c r="B135" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="C135" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="D135" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="E135" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="F135" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="G135" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="H135" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="I135" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="J135" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="K135" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="L135" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="M135" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="N135" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="O135" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="P135" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="Q135" t="n">
+        <v>0.21244</v>
+      </c>
+      <c r="R135" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="S135" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="T135" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="U135" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="V135" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="W135" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="X135" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="Y135" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="Z135" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AA135" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AB135" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AC135" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AD135" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AE135" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AF135" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AG135" t="n">
+        <v>0.17362</v>
+      </c>
+      <c r="AH135" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AI135" t="n">
+        <v>0.21218</v>
+      </c>
+      <c r="AJ135" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AK135" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AL135" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AM135" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AN135" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AO135" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AP135" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AQ135" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AR135" t="n">
+        <v>-0.04295</v>
+      </c>
+      <c r="AS135" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AT135" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AU135" t="n">
+        <v>0.12623</v>
+      </c>
+      <c r="AV135" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AW135" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AX135" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AY135" t="n">
+        <v>0.26918</v>
+      </c>
+      <c r="AZ135" t="n">
+        <v>0.25488</v>
+      </c>
+      <c r="BA135" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BB135" t="n">
+        <v>-0.02842</v>
+      </c>
+      <c r="BC135" t="n">
+        <v>0.27435</v>
+      </c>
+      <c r="BD135" t="n">
+        <v>0.23994</v>
+      </c>
+      <c r="BE135" t="n">
+        <v>0.22279</v>
+      </c>
+      <c r="BF135" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BG135" t="n">
+        <v>0.16145</v>
+      </c>
+      <c r="BH135" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BI135" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BJ135" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BK135" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BL135" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BM135" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BN135" t="n">
+        <v>0.11025</v>
+      </c>
+      <c r="BO135" t="n">
+        <v>0.11558</v>
+      </c>
+      <c r="BP135" t="n">
+        <v>0.08799999999999999</v>
+      </c>
+      <c r="BQ135" t="n">
+        <v>0.12997</v>
+      </c>
+      <c r="BR135" t="n">
+        <v>0.21469</v>
+      </c>
+      <c r="BS135" t="n">
+        <v>0.04776</v>
+      </c>
+      <c r="BT135" t="n">
+        <v>0.12276</v>
+      </c>
+      <c r="BU135" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BV135" t="n">
+        <v>-0.04051</v>
+      </c>
+      <c r="BW135" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BX135" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BY135" t="n">
+        <v>0.04136</v>
+      </c>
+      <c r="BZ135" t="n">
+        <v>0.17624</v>
+      </c>
+      <c r="CA135" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="CB135" t="n">
+        <v>-0.01212</v>
+      </c>
+      <c r="CC135" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="CD135" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="CE135" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="CF135" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="CG135" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="CH135" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="CI135" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="CJ135" t="n">
+        <v>-0.04742</v>
+      </c>
+      <c r="CK135" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="CL135" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="CM135" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="CN135" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="CO135" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="CP135" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="CQ135" t="n">
+        <v>0.01921</v>
+      </c>
+      <c r="CR135" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="CS135" t="n">
+        <v>-0.05</v>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" s="2" t="n">
+        <v>46159</v>
+      </c>
+      <c r="B136" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="C136" t="n">
+        <v>-0.03453</v>
+      </c>
+      <c r="D136" t="n">
+        <v>0.0575</v>
+      </c>
+      <c r="E136" t="n">
+        <v>0.04811</v>
+      </c>
+      <c r="F136" t="n">
+        <v>0.0569</v>
+      </c>
+      <c r="G136" t="n">
+        <v>0.03011</v>
+      </c>
+      <c r="H136" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="I136" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="J136" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="K136" t="n">
+        <v>0.08241</v>
+      </c>
+      <c r="L136" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="M136" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="N136" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="O136" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="P136" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="Q136" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="R136" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="S136" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="T136" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="U136" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="V136" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="W136" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="X136" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="Y136" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="Z136" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AA136" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AB136" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AC136" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AD136" t="n">
+        <v>0.19709</v>
+      </c>
+      <c r="AE136" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AF136" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AG136" t="n">
+        <v>0.1368</v>
+      </c>
+      <c r="AH136" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AI136" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AJ136" t="n">
+        <v>0.00042</v>
+      </c>
+      <c r="AK136" t="n">
+        <v>0.00087</v>
+      </c>
+      <c r="AL136" t="n">
+        <v>-0.04959</v>
+      </c>
+      <c r="AM136" t="n">
+        <v>0.15611</v>
+      </c>
+      <c r="AN136" t="n">
+        <v>0.0227</v>
+      </c>
+      <c r="AO136" t="n">
+        <v>-0.03959</v>
+      </c>
+      <c r="AP136" t="n">
+        <v>-0.04961</v>
+      </c>
+      <c r="AQ136" t="n">
+        <v>-0.01429</v>
+      </c>
+      <c r="AR136" t="n">
+        <v>-0.04307</v>
+      </c>
+      <c r="AS136" t="n">
+        <v>-0.04102</v>
+      </c>
+      <c r="AT136" t="n">
+        <v>-0.04863</v>
+      </c>
+      <c r="AU136" t="n">
+        <v>-0.04829</v>
+      </c>
+      <c r="AV136" t="n">
+        <v>-0.02445</v>
+      </c>
+      <c r="AW136" t="n">
+        <v>-0.02946</v>
+      </c>
+      <c r="AX136" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AY136" t="n">
+        <v>-0.04963</v>
+      </c>
+      <c r="AZ136" t="n">
+        <v>-0.03835</v>
+      </c>
+      <c r="BA136" t="n">
+        <v>-0.04961</v>
+      </c>
+      <c r="BB136" t="n">
+        <v>-0.04962</v>
+      </c>
+      <c r="BC136" t="n">
+        <v>-0.04942</v>
+      </c>
+      <c r="BD136" t="n">
+        <v>0.00267</v>
+      </c>
+      <c r="BE136" t="n">
+        <v>0.28016</v>
+      </c>
+      <c r="BF136" t="n">
+        <v>-0.04966</v>
+      </c>
+      <c r="BG136" t="n">
+        <v>-0.04929</v>
+      </c>
+      <c r="BH136" t="n">
+        <v>-0.04962</v>
+      </c>
+      <c r="BI136" t="n">
+        <v>-0.03561</v>
+      </c>
+      <c r="BJ136" t="n">
+        <v>-0.01149</v>
+      </c>
+      <c r="BK136" t="n">
+        <v>-0.0496</v>
+      </c>
+      <c r="BL136" t="n">
+        <v>-0.04966</v>
+      </c>
+      <c r="BM136" t="n">
+        <v>-0.03528</v>
+      </c>
+      <c r="BN136" t="n">
+        <v>0.20796</v>
+      </c>
+      <c r="BO136" t="n">
+        <v>0.27021</v>
+      </c>
+      <c r="BP136" t="n">
+        <v>0.29413</v>
+      </c>
+      <c r="BQ136" t="n">
+        <v>0.28187</v>
+      </c>
+      <c r="BR136" t="n">
+        <v>0.16818</v>
+      </c>
+      <c r="BS136" t="n">
+        <v>0.20805</v>
+      </c>
+      <c r="BT136" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BU136" t="n">
+        <v>0.18407</v>
+      </c>
+      <c r="BV136" t="n">
+        <v>0.13905</v>
+      </c>
+      <c r="BW136" t="n">
+        <v>0.21598</v>
+      </c>
+      <c r="BX136" t="n">
+        <v>0.20859</v>
+      </c>
+      <c r="BY136" t="n">
+        <v>0.14765</v>
+      </c>
+      <c r="BZ136" t="n">
+        <v>0.14201</v>
+      </c>
+      <c r="CA136" t="n">
+        <v>0.20179</v>
+      </c>
+      <c r="CB136" t="n">
+        <v>0.10898</v>
+      </c>
+      <c r="CC136" t="n">
+        <v>0.08887</v>
+      </c>
+      <c r="CD136" t="n">
+        <v>0.06251</v>
+      </c>
+      <c r="CE136" t="n">
+        <v>0.21201</v>
+      </c>
+      <c r="CF136" t="n">
+        <v>0.20926</v>
+      </c>
+      <c r="CG136" t="n">
+        <v>0.12903</v>
+      </c>
+      <c r="CH136" t="n">
+        <v>0.10267</v>
+      </c>
+      <c r="CI136" t="n">
+        <v>0.09323000000000001</v>
+      </c>
+      <c r="CJ136" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="CK136" t="n">
+        <v>0.16687</v>
+      </c>
+      <c r="CL136" t="n">
+        <v>0.06703000000000001</v>
+      </c>
+      <c r="CM136" t="n">
+        <v>0.15263</v>
+      </c>
+      <c r="CN136" t="n">
+        <v>0.1336</v>
+      </c>
+      <c r="CO136" t="n">
+        <v>0.11873</v>
+      </c>
+      <c r="CP136" t="n">
+        <v>0.08624999999999999</v>
+      </c>
+      <c r="CQ136" t="n">
+        <v>0.14936</v>
+      </c>
+      <c r="CR136" t="n">
+        <v>0.19745</v>
+      </c>
+      <c r="CS136" t="n">
+        <v>-0.03118</v>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" s="2" t="n">
+        <v>46160</v>
+      </c>
+      <c r="B137" t="n">
+        <v>0.29801</v>
+      </c>
+      <c r="C137" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="D137" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="E137" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="F137" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="G137" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="H137" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="I137" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="J137" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="K137" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="L137" t="n">
+        <v>0.21164</v>
+      </c>
+      <c r="M137" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="N137" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="O137" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="P137" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="Q137" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="R137" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="S137" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="T137" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="U137" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="V137" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="W137" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="X137" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="Y137" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="Z137" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AA137" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AB137" t="n">
+        <v>0.30765</v>
+      </c>
+      <c r="AC137" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AD137" t="n">
+        <v>-0.02646</v>
+      </c>
+      <c r="AE137" t="n">
+        <v>0.21679</v>
+      </c>
+      <c r="AF137" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AG137" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AH137" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AI137" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AJ137" t="n">
+        <v>0.75271</v>
+      </c>
+      <c r="AK137" t="n">
+        <v>0.87148</v>
+      </c>
+      <c r="AL137" t="n">
+        <v>0.33176</v>
+      </c>
+      <c r="AM137" t="n">
+        <v>0.24358</v>
+      </c>
+      <c r="AN137" t="n">
+        <v>0.03958</v>
+      </c>
+      <c r="AO137" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AP137" t="n">
+        <v>0.16789</v>
+      </c>
+      <c r="AQ137" t="n">
+        <v>-0.04852</v>
+      </c>
+      <c r="AR137" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AS137" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AT137" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AU137" t="n">
+        <v>-0.00222</v>
+      </c>
+      <c r="AV137" t="n">
+        <v>-0.04515</v>
+      </c>
+      <c r="AW137" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AX137" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AY137" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AZ137" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BA137" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BB137" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BC137" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BD137" t="n">
+        <v>0.29841</v>
+      </c>
+      <c r="BE137" t="n">
+        <v>0.32395</v>
+      </c>
+      <c r="BF137" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BG137" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BH137" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BI137" t="n">
+        <v>0.30578</v>
+      </c>
+      <c r="BJ137" t="n">
+        <v>-0.04554</v>
+      </c>
+      <c r="BK137" t="n">
+        <v>0.31296</v>
+      </c>
+      <c r="BL137" t="n">
+        <v>0.25442</v>
+      </c>
+      <c r="BM137" t="n">
+        <v>0.29183</v>
+      </c>
+      <c r="BN137" t="n">
+        <v>0.37993</v>
+      </c>
+      <c r="BO137" t="n">
+        <v>0.32009</v>
+      </c>
+      <c r="BP137" t="n">
+        <v>0.28948</v>
+      </c>
+      <c r="BQ137" t="n">
+        <v>0.23471</v>
+      </c>
+      <c r="BR137" t="n">
+        <v>0.1004</v>
+      </c>
+      <c r="BS137" t="n">
+        <v>0.06708</v>
+      </c>
+      <c r="BT137" t="n">
+        <v>0.17886</v>
+      </c>
+      <c r="BU137" t="n">
+        <v>0.14315</v>
+      </c>
+      <c r="BV137" t="n">
+        <v>0.15493</v>
+      </c>
+      <c r="BW137" t="n">
+        <v>0.06881</v>
+      </c>
+      <c r="BX137" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BY137" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BZ137" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="CA137" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="CB137" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="CC137" t="n">
+        <v>0.84084</v>
+      </c>
+      <c r="CD137" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="CE137" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="CF137" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="CG137" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CH137" t="n">
+        <v>0.70317</v>
+      </c>
+      <c r="CI137" t="n">
+        <v>0.7014199999999999</v>
+      </c>
+      <c r="CJ137" t="n">
+        <v>0.7055399999999999</v>
+      </c>
+      <c r="CK137" t="n">
+        <v>0.8019500000000001</v>
+      </c>
+      <c r="CL137" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="CM137" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="CN137" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="CO137" t="n">
+        <v>0.18492</v>
+      </c>
+      <c r="CP137" t="n">
+        <v>0.15339</v>
+      </c>
+      <c r="CQ137" t="n">
+        <v>0.23955</v>
+      </c>
+      <c r="CR137" t="n">
+        <v>0.05314</v>
+      </c>
+      <c r="CS137" t="n">
+        <v>0.05298</v>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" s="2" t="n">
+        <v>46161</v>
+      </c>
+      <c r="B138" t="n">
+        <v>0.33007</v>
+      </c>
+      <c r="C138" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="D138" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="E138" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="F138" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="G138" t="n">
+        <v>0.36054</v>
+      </c>
+      <c r="H138" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="I138" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="J138" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="K138" t="n">
+        <v>0.24842</v>
+      </c>
+      <c r="L138" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="M138" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="N138" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="O138" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="P138" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="Q138" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="R138" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="S138" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="T138" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="U138" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="V138" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="W138" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="X138" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="Y138" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="Z138" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AA138" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AB138" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AC138" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AD138" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AE138" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AF138" t="n">
+        <v>0.18871</v>
+      </c>
+      <c r="AG138" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AH138" t="n">
+        <v>0.08854000000000001</v>
+      </c>
+      <c r="AI138" t="n">
+        <v>0.08636000000000001</v>
+      </c>
+      <c r="AJ138" t="n">
+        <v>0.29509</v>
+      </c>
+      <c r="AK138" t="n">
+        <v>0.07723000000000001</v>
+      </c>
+      <c r="AL138" t="n">
+        <v>0.23695</v>
+      </c>
+      <c r="AM138" t="n">
+        <v>0.31597</v>
+      </c>
+      <c r="AN138" t="n">
+        <v>0.12448</v>
+      </c>
+      <c r="AO138" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AP138" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AQ138" t="n">
+        <v>-0.04811</v>
+      </c>
+      <c r="AR138" t="n">
+        <v>0.10998</v>
+      </c>
+      <c r="AS138" t="n">
+        <v>0.25306</v>
+      </c>
+      <c r="AT138" t="n">
+        <v>0.28432</v>
+      </c>
+      <c r="AU138" t="n">
+        <v>0.30074</v>
+      </c>
+      <c r="AV138" t="n">
+        <v>0.28987</v>
+      </c>
+      <c r="AW138" t="n">
+        <v>0.3096</v>
+      </c>
+      <c r="AX138" t="n">
+        <v>0.2598</v>
+      </c>
+      <c r="AY138" t="n">
+        <v>0.31226</v>
+      </c>
+      <c r="AZ138" t="n">
+        <v>0.30349</v>
+      </c>
+      <c r="BA138" t="n">
+        <v>0.30337</v>
+      </c>
+      <c r="BB138" t="n">
+        <v>0.32674</v>
+      </c>
+      <c r="BC138" t="n">
+        <v>0.32135</v>
+      </c>
+      <c r="BD138" t="n">
+        <v>0.31912</v>
+      </c>
+      <c r="BE138" t="n">
+        <v>0.22444</v>
+      </c>
+      <c r="BF138" t="n">
+        <v>0.31854</v>
+      </c>
+      <c r="BG138" t="n">
+        <v>0.32581</v>
+      </c>
+      <c r="BH138" t="n">
+        <v>0.31561</v>
+      </c>
+      <c r="BI138" t="n">
+        <v>0.28634</v>
+      </c>
+      <c r="BJ138" t="n">
+        <v>0.32279</v>
+      </c>
+      <c r="BK138" t="n">
+        <v>0.24841</v>
+      </c>
+      <c r="BL138" t="n">
+        <v>0.2378</v>
+      </c>
+      <c r="BM138" t="n">
+        <v>0.30166</v>
+      </c>
+      <c r="BN138" t="n">
+        <v>0.29626</v>
+      </c>
+      <c r="BO138" t="n">
+        <v>0.32441</v>
+      </c>
+      <c r="BP138" t="n">
+        <v>0.25117</v>
+      </c>
+      <c r="BQ138" t="n">
+        <v>0.23397</v>
+      </c>
+      <c r="BR138" t="n">
+        <v>0.23844</v>
+      </c>
+      <c r="BS138" t="n">
+        <v>0.21008</v>
+      </c>
+      <c r="BT138" t="n">
+        <v>0.23304</v>
+      </c>
+      <c r="BU138" t="n">
+        <v>0.19837</v>
+      </c>
+      <c r="BV138" t="n">
+        <v>0.30666</v>
+      </c>
+      <c r="BW138" t="n">
+        <v>0.22481</v>
+      </c>
+      <c r="BX138" t="n">
+        <v>0.31243</v>
+      </c>
+      <c r="BY138" t="n">
+        <v>0.18657</v>
+      </c>
+      <c r="BZ138" t="n">
+        <v>0.1518</v>
+      </c>
+      <c r="CA138" t="n">
+        <v>0.30062</v>
+      </c>
+      <c r="CB138" t="n">
+        <v>0.17599</v>
+      </c>
+      <c r="CC138" t="n">
+        <v>0.12069</v>
+      </c>
+      <c r="CD138" t="n">
+        <v>0.29143</v>
+      </c>
+      <c r="CE138" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="CF138" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="CG138" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="CH138" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="CI138" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="CJ138" t="n">
+        <v>0.00744</v>
+      </c>
+      <c r="CK138" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="CL138" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="CM138" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="CN138" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="CO138" t="n">
+        <v>0.0948</v>
+      </c>
+      <c r="CP138" t="n">
+        <v>0.03304</v>
+      </c>
+      <c r="CQ138" t="n">
+        <v>0.05241</v>
+      </c>
+      <c r="CR138" t="n">
+        <v>0.009439999999999999</v>
+      </c>
+      <c r="CS138" t="n">
+        <v>0.03335</v>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" s="2" t="n">
+        <v>46162</v>
+      </c>
+      <c r="B139" t="n">
+        <v>0.3271</v>
+      </c>
+      <c r="C139" t="n">
+        <v>0.06099</v>
+      </c>
+      <c r="D139" t="n">
+        <v>-0.00243</v>
+      </c>
+      <c r="E139" t="n">
+        <v>0.0494</v>
+      </c>
+      <c r="F139" t="n">
+        <v>-0.00498</v>
+      </c>
+      <c r="G139" t="n">
+        <v>0.05097</v>
+      </c>
+      <c r="H139" t="n">
+        <v>0.05553</v>
+      </c>
+      <c r="I139" t="n">
+        <v>0.07262</v>
+      </c>
+      <c r="J139" t="n">
+        <v>0.13366</v>
+      </c>
+      <c r="K139" t="n">
+        <v>0.09085</v>
+      </c>
+      <c r="L139" t="n">
+        <v>0.09418000000000001</v>
+      </c>
+      <c r="M139" t="n">
+        <v>0.09394</v>
+      </c>
+      <c r="N139" t="n">
+        <v>0.2167</v>
+      </c>
+      <c r="O139" t="n">
+        <v>0.12493</v>
+      </c>
+      <c r="P139" t="n">
+        <v>0.13853</v>
+      </c>
+      <c r="Q139" t="n">
+        <v>0.21225</v>
+      </c>
+      <c r="R139" t="n">
+        <v>0.09337000000000001</v>
+      </c>
+      <c r="S139" t="n">
+        <v>0.11103</v>
+      </c>
+      <c r="T139" t="n">
+        <v>0.11333</v>
+      </c>
+      <c r="U139" t="n">
+        <v>0.09684999999999999</v>
+      </c>
+      <c r="V139" t="n">
+        <v>0.10986</v>
+      </c>
+      <c r="W139" t="n">
+        <v>0.11621</v>
+      </c>
+      <c r="X139" t="n">
+        <v>0.11629</v>
+      </c>
+      <c r="Y139" t="n">
+        <v>0.10058</v>
+      </c>
+      <c r="Z139" t="n">
+        <v>0.11317</v>
+      </c>
+      <c r="AA139" t="n">
+        <v>0.09261</v>
+      </c>
+      <c r="AB139" t="n">
+        <v>0.10021</v>
+      </c>
+      <c r="AC139" t="n">
+        <v>0.09333</v>
+      </c>
+      <c r="AD139" t="n">
+        <v>0.132</v>
+      </c>
+      <c r="AE139" t="n">
+        <v>0.11947</v>
+      </c>
+      <c r="AF139" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AG139" t="n">
+        <v>0.03615</v>
+      </c>
+      <c r="AH139" t="n">
+        <v>0.06765</v>
+      </c>
+      <c r="AI139" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AJ139" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AK139" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AL139" t="n">
+        <v>0.27092</v>
+      </c>
+      <c r="AM139" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AN139" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AO139" t="n">
+        <v>0.09196</v>
+      </c>
+      <c r="AP139" t="n">
+        <v>0.16858</v>
+      </c>
+      <c r="AQ139" t="n">
+        <v>0.24317</v>
+      </c>
+      <c r="AR139" t="n">
+        <v>0.25365</v>
+      </c>
+      <c r="AS139" t="n">
+        <v>0.2252</v>
+      </c>
+      <c r="AT139" t="n">
+        <v>0.18787</v>
+      </c>
+      <c r="AU139" t="n">
+        <v>0.22278</v>
+      </c>
+      <c r="AV139" t="n">
+        <v>0.23971</v>
+      </c>
+      <c r="AW139" t="n">
+        <v>0.24711</v>
+      </c>
+      <c r="AX139" t="n">
+        <v>0.25954</v>
+      </c>
+      <c r="AY139" t="n">
+        <v>0.21131</v>
+      </c>
+      <c r="AZ139" t="n">
+        <v>0.30302</v>
+      </c>
+      <c r="BA139" t="n">
+        <v>0.25941</v>
+      </c>
+      <c r="BB139" t="n">
+        <v>0.30637</v>
+      </c>
+      <c r="BC139" t="n">
+        <v>0.31338</v>
+      </c>
+      <c r="BD139" t="n">
+        <v>0.28854</v>
+      </c>
+      <c r="BE139" t="n">
+        <v>0.35445</v>
+      </c>
+      <c r="BF139" t="n">
+        <v>0.32528</v>
+      </c>
+      <c r="BG139" t="n">
+        <v>0.32264</v>
+      </c>
+      <c r="BH139" t="n">
+        <v>0.313</v>
+      </c>
+      <c r="BI139" t="n">
+        <v>0.33026</v>
+      </c>
+      <c r="BJ139" t="n">
+        <v>0.32839</v>
+      </c>
+      <c r="BK139" t="n">
+        <v>0.3328</v>
+      </c>
+      <c r="BL139" t="n">
+        <v>0.32203</v>
+      </c>
+      <c r="BM139" t="n">
+        <v>0.23957</v>
+      </c>
+      <c r="BN139" t="n">
+        <v>0.26742</v>
+      </c>
+      <c r="BO139" t="n">
+        <v>0.30379</v>
+      </c>
+      <c r="BP139" t="n">
+        <v>0.40452</v>
+      </c>
+      <c r="BQ139" t="n">
+        <v>0.40987</v>
+      </c>
+      <c r="BR139" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BS139" t="n">
+        <v>0.68501</v>
+      </c>
+      <c r="BT139" t="n">
+        <v>0.4704700000000001</v>
+      </c>
+      <c r="BU139" t="n">
+        <v>0.12372</v>
+      </c>
+      <c r="BV139" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BW139" t="n">
+        <v>0.4117</v>
+      </c>
+      <c r="BX139" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BY139" t="n">
+        <v>0.83075</v>
+      </c>
+      <c r="BZ139" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="CA139" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="CB139" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="CC139" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="CD139" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="CE139" t="n">
+        <v>0.29446</v>
+      </c>
+      <c r="CF139" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="CG139" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="CH139" t="n">
+        <v>0.05556000000000001</v>
+      </c>
+      <c r="CI139" t="n">
+        <v>0.23944</v>
+      </c>
+      <c r="CJ139" t="n">
+        <v>0.22317</v>
+      </c>
+      <c r="CK139" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="CL139" t="n">
+        <v>0.05175</v>
+      </c>
+      <c r="CM139" t="n">
+        <v>0.16091</v>
+      </c>
+      <c r="CN139" t="n">
+        <v>0.06347999999999999</v>
+      </c>
+      <c r="CO139" t="n">
+        <v>0.12726</v>
+      </c>
+      <c r="CP139" t="n">
+        <v>0.0116</v>
+      </c>
+      <c r="CQ139" t="n">
+        <v>0.11536</v>
+      </c>
+      <c r="CR139" t="n">
+        <v>0.10518</v>
+      </c>
+      <c r="CS139" t="n">
+        <v>0.11709</v>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" s="2" t="n">
+        <v>46163</v>
+      </c>
+      <c r="B140" t="n">
+        <v>0.20868</v>
+      </c>
+      <c r="C140" t="n">
+        <v>0.09622</v>
+      </c>
+      <c r="D140" t="n">
+        <v>0.09595999999999999</v>
+      </c>
+      <c r="E140" t="n">
+        <v>0.03477</v>
+      </c>
+      <c r="F140" t="n">
+        <v>0.05176</v>
+      </c>
+      <c r="G140" t="n">
+        <v>0.07734000000000001</v>
+      </c>
+      <c r="H140" t="n">
+        <v>0.14452</v>
+      </c>
+      <c r="I140" t="n">
+        <v>0.07908</v>
+      </c>
+      <c r="J140" t="n">
+        <v>0.23615</v>
+      </c>
+      <c r="K140" t="n">
+        <v>0.09938</v>
+      </c>
+      <c r="L140" t="n">
+        <v>0.09845999999999999</v>
+      </c>
+      <c r="M140" t="n">
+        <v>0.09156</v>
+      </c>
+      <c r="N140" t="n">
+        <v>0.13091</v>
+      </c>
+      <c r="O140" t="n">
+        <v>0.15031</v>
+      </c>
+      <c r="P140" t="n">
+        <v>0.14288</v>
+      </c>
+      <c r="Q140" t="n">
+        <v>0.14434</v>
+      </c>
+      <c r="R140" t="n">
+        <v>0.1437</v>
+      </c>
+      <c r="S140" t="n">
+        <v>0.1128</v>
+      </c>
+      <c r="T140" t="n">
+        <v>0.20119</v>
+      </c>
+      <c r="U140" t="n">
+        <v>0.10528</v>
+      </c>
+      <c r="V140" t="n">
+        <v>0.10592</v>
+      </c>
+      <c r="W140" t="n">
+        <v>0.10392</v>
+      </c>
+      <c r="X140" t="n">
+        <v>0.08734</v>
+      </c>
+      <c r="Y140" t="n">
+        <v>0.21138</v>
+      </c>
+      <c r="Z140" t="n">
+        <v>0.03497</v>
+      </c>
+      <c r="AA140" t="n">
+        <v>0.05077</v>
+      </c>
+      <c r="AB140" t="n">
+        <v>-0.04469</v>
+      </c>
+      <c r="AC140" t="n">
+        <v>0.02715</v>
+      </c>
+      <c r="AD140" t="n">
+        <v>0.22733</v>
+      </c>
+      <c r="AE140" t="n">
+        <v>0.11069</v>
+      </c>
+      <c r="AF140" t="n">
+        <v>0.19453</v>
+      </c>
+      <c r="AG140" t="n">
+        <v>0.19029</v>
+      </c>
+      <c r="AH140" t="n">
+        <v>0.10853</v>
+      </c>
+      <c r="AI140" t="n">
+        <v>0.22389</v>
+      </c>
+      <c r="AJ140" t="n">
+        <v>0.39064</v>
+      </c>
+      <c r="AK140" t="n">
+        <v>0.205</v>
+      </c>
+      <c r="AL140" t="n">
+        <v>0.35337</v>
+      </c>
+      <c r="AM140" t="n">
+        <v>0.43417</v>
+      </c>
+      <c r="AN140" t="n">
+        <v>0.37931</v>
+      </c>
+      <c r="AO140" t="n">
+        <v>0.20567</v>
+      </c>
+      <c r="AP140" t="n">
+        <v>0.23102</v>
+      </c>
+      <c r="AQ140" t="n">
+        <v>0.19852</v>
+      </c>
+      <c r="AR140" t="n">
+        <v>0.3104</v>
+      </c>
+      <c r="AS140" t="n">
+        <v>0.36358</v>
+      </c>
+      <c r="AT140" t="n">
+        <v>0.25294</v>
+      </c>
+      <c r="AU140" t="n">
+        <v>0.16144</v>
+      </c>
+      <c r="AV140" t="n">
+        <v>0.16121</v>
+      </c>
+      <c r="AW140" t="n">
+        <v>0.17954</v>
+      </c>
+      <c r="AX140" t="n">
+        <v>0.29265</v>
+      </c>
+      <c r="AY140" t="n">
+        <v>0.33249</v>
+      </c>
+      <c r="AZ140" t="n">
+        <v>0.33431</v>
+      </c>
+      <c r="BA140" t="n">
+        <v>0.32877</v>
+      </c>
+      <c r="BB140" t="n">
+        <v>0.32464</v>
+      </c>
+      <c r="BC140" t="n">
+        <v>0.31639</v>
+      </c>
+      <c r="BD140" t="n">
+        <v>0.33682</v>
+      </c>
+      <c r="BE140" t="n">
+        <v>0.3437</v>
+      </c>
+      <c r="BF140" t="n">
+        <v>0.32534</v>
+      </c>
+      <c r="BG140" t="n">
+        <v>0.33335</v>
+      </c>
+      <c r="BH140" t="n">
+        <v>0.34129</v>
+      </c>
+      <c r="BI140" t="n">
+        <v>0.33779</v>
+      </c>
+      <c r="BJ140" t="n">
+        <v>0.32478</v>
+      </c>
+      <c r="BK140" t="n">
+        <v>0.34411</v>
+      </c>
+      <c r="BL140" t="n">
+        <v>0.30607</v>
+      </c>
+      <c r="BM140" t="n">
+        <v>0.13109</v>
+      </c>
+      <c r="BN140" t="n">
+        <v>0.19002</v>
+      </c>
+      <c r="BO140" t="n">
+        <v>0.22027</v>
+      </c>
+      <c r="BP140" t="n">
+        <v>0.37027</v>
+      </c>
+      <c r="BQ140" t="n">
+        <v>0.19074</v>
+      </c>
+      <c r="BR140" t="n">
+        <v>0.19584</v>
+      </c>
+      <c r="BS140" t="n">
+        <v>0.22549</v>
+      </c>
+      <c r="BT140" t="n">
+        <v>0.17592</v>
+      </c>
+      <c r="BU140" t="n">
+        <v>0.26101</v>
+      </c>
+      <c r="BV140" t="n">
+        <v>0.17269</v>
+      </c>
+      <c r="BW140" t="n">
+        <v>0.45423</v>
+      </c>
+      <c r="BX140" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BY140" t="n">
+        <v>0.6349400000000001</v>
+      </c>
+      <c r="BZ140" t="n">
+        <v>0.4499</v>
+      </c>
+      <c r="CA140" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="CB140" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="CC140" t="n">
+        <v>0.1073</v>
+      </c>
+      <c r="CD140" t="n">
+        <v>0.13936</v>
+      </c>
+      <c r="CE140" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="CF140" t="n">
+        <v>0.10778</v>
+      </c>
+      <c r="CG140" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="CH140" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="CI140" t="n">
+        <v>0.8158200000000001</v>
+      </c>
+      <c r="CJ140" t="n">
+        <v>0.72123</v>
+      </c>
+      <c r="CK140" t="n">
+        <v>0.35111</v>
+      </c>
+      <c r="CL140" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="CM140" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="CN140" t="n">
+        <v>0.04875</v>
+      </c>
+      <c r="CO140" t="n">
+        <v>0.04206</v>
+      </c>
+      <c r="CP140" t="n">
+        <v>0.10378</v>
+      </c>
+      <c r="CQ140" t="n">
+        <v>0.11152</v>
+      </c>
+      <c r="CR140" t="n">
+        <v>0.08979999999999999</v>
+      </c>
+      <c r="CS140" t="n">
+        <v>0.07253</v>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" s="2" t="n">
+        <v>46164</v>
+      </c>
+      <c r="B141" t="n">
+        <v>0.16884</v>
+      </c>
+      <c r="C141" t="n">
+        <v>0.13944</v>
+      </c>
+      <c r="D141" t="n">
+        <v>0.20411</v>
+      </c>
+      <c r="E141" t="n">
+        <v>0.03904</v>
+      </c>
+      <c r="F141" t="n">
+        <v>0.19418</v>
+      </c>
+      <c r="G141" t="n">
+        <v>0.18417</v>
+      </c>
+      <c r="H141" t="n">
+        <v>-0.01988</v>
+      </c>
+      <c r="I141" t="n">
+        <v>-0.009820000000000001</v>
+      </c>
+      <c r="J141" t="n">
+        <v>-0.01212</v>
+      </c>
+      <c r="K141" t="n">
+        <v>0.06238</v>
+      </c>
+      <c r="L141" t="n">
+        <v>0.18736</v>
+      </c>
+      <c r="M141" t="n">
+        <v>0.05805</v>
+      </c>
+      <c r="N141" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="O141" t="n">
+        <v>0.18731</v>
+      </c>
+      <c r="P141" t="n">
+        <v>0.17631</v>
+      </c>
+      <c r="Q141" t="n">
+        <v>0.02698</v>
+      </c>
+      <c r="R141" t="n">
+        <v>0.05212</v>
+      </c>
+      <c r="S141" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="T141" t="n">
+        <v>0.02307</v>
+      </c>
+      <c r="U141" t="n">
+        <v>0.01267</v>
+      </c>
+      <c r="V141" t="n">
+        <v>0.18315</v>
+      </c>
+      <c r="W141" t="n">
+        <v>-0.03178</v>
+      </c>
+      <c r="X141" t="n">
+        <v>0.17804</v>
+      </c>
+      <c r="Y141" t="n">
+        <v>0.19176</v>
+      </c>
+      <c r="Z141" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AA141" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AB141" t="n">
+        <v>0.21971</v>
+      </c>
+      <c r="AC141" t="n">
+        <v>0.22111</v>
+      </c>
+      <c r="AD141" t="n">
+        <v>0.19889</v>
+      </c>
+      <c r="AE141" t="n">
+        <v>0.04809</v>
+      </c>
+      <c r="AF141" t="n">
+        <v>0.05193</v>
+      </c>
+      <c r="AG141" t="n">
+        <v>0.30051</v>
+      </c>
+      <c r="AH141" t="n">
+        <v>0.27904</v>
+      </c>
+      <c r="AI141" t="n">
+        <v>0.31431</v>
+      </c>
+      <c r="AJ141" t="n">
+        <v>0.30954</v>
+      </c>
+      <c r="AK141" t="n">
+        <v>0.31354</v>
+      </c>
+      <c r="AL141" t="n">
+        <v>0.32153</v>
+      </c>
+      <c r="AM141" t="n">
+        <v>0.32234</v>
+      </c>
+      <c r="AN141" t="n">
+        <v>0.34285</v>
+      </c>
+      <c r="AO141" t="n">
+        <v>0.24433</v>
+      </c>
+      <c r="AP141" t="n">
+        <v>0.31085</v>
+      </c>
+      <c r="AQ141" t="n">
+        <v>0.30267</v>
+      </c>
+      <c r="AR141" t="n">
+        <v>0.20937</v>
+      </c>
+      <c r="AS141" t="n">
+        <v>0.36514</v>
+      </c>
+      <c r="AT141" t="n">
+        <v>0.34171</v>
+      </c>
+      <c r="AU141" t="n">
+        <v>0.33734</v>
+      </c>
+      <c r="AV141" t="n">
+        <v>0.19817</v>
+      </c>
+      <c r="AW141" t="n">
+        <v>0.24999</v>
+      </c>
+      <c r="AX141" t="n">
+        <v>-0.03207</v>
+      </c>
+      <c r="AY141" t="n">
+        <v>0.17491</v>
+      </c>
+      <c r="AZ141" t="n">
+        <v>0.30728</v>
+      </c>
+      <c r="BA141" t="n">
+        <v>0.27731</v>
+      </c>
+      <c r="BB141" t="n">
+        <v>0.0317</v>
+      </c>
+      <c r="BC141" t="n">
+        <v>-0.01894</v>
+      </c>
+      <c r="BD141" t="n">
+        <v>0.17881</v>
+      </c>
+      <c r="BE141" t="n">
+        <v>0.19553</v>
+      </c>
+      <c r="BF141" t="n">
+        <v>0.03573</v>
+      </c>
+      <c r="BG141" t="n">
+        <v>0.05775</v>
+      </c>
+      <c r="BH141" t="n">
+        <v>0.30775</v>
+      </c>
+      <c r="BI141" t="n">
+        <v>0.27628</v>
+      </c>
+      <c r="BJ141" t="n">
+        <v>0.23571</v>
+      </c>
+      <c r="BK141" t="n">
+        <v>0.25248</v>
+      </c>
+      <c r="BL141" t="n">
+        <v>0.32604</v>
+      </c>
+      <c r="BM141" t="n">
+        <v>0.34966</v>
+      </c>
+      <c r="BN141" t="n">
+        <v>0.33146</v>
+      </c>
+      <c r="BO141" t="n">
+        <v>0.32632</v>
+      </c>
+      <c r="BP141" t="n">
+        <v>0.32808</v>
+      </c>
+      <c r="BQ141" t="n">
+        <v>0.32996</v>
+      </c>
+      <c r="BR141" t="n">
+        <v>0.3013</v>
+      </c>
+      <c r="BS141" t="n">
+        <v>0.31823</v>
+      </c>
+      <c r="BT141" t="n">
+        <v>0.33164</v>
+      </c>
+      <c r="BU141" t="n">
+        <v>0.31532</v>
+      </c>
+      <c r="BV141" t="n">
+        <v>0.33362</v>
+      </c>
+      <c r="BW141" t="n">
+        <v>0.34854</v>
+      </c>
+      <c r="BX141" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BY141" t="n">
+        <v>0.42507</v>
+      </c>
+      <c r="BZ141" t="n">
+        <v>0.30049</v>
+      </c>
+      <c r="CA141" t="n">
+        <v>0.39282</v>
+      </c>
+      <c r="CB141" t="n">
+        <v>0.43173</v>
+      </c>
+      <c r="CC141" t="n">
+        <v>0.39924</v>
+      </c>
+      <c r="CD141" t="n">
+        <v>0.35182</v>
+      </c>
+      <c r="CE141" t="n">
+        <v>0.36876</v>
+      </c>
+      <c r="CF141" t="n">
+        <v>0.41226</v>
+      </c>
+      <c r="CG141" t="n">
+        <v>0.42229</v>
+      </c>
+      <c r="CH141" t="n">
+        <v>0.35296</v>
+      </c>
+      <c r="CI141" t="n">
+        <v>0.4372</v>
+      </c>
+      <c r="CJ141" t="n">
+        <v>0.37491</v>
+      </c>
+      <c r="CK141" t="n">
+        <v>0.351</v>
+      </c>
+      <c r="CL141" t="n">
+        <v>0.34983</v>
+      </c>
+      <c r="CM141" t="n">
+        <v>0.35044</v>
+      </c>
+      <c r="CN141" t="n">
+        <v>0.32543</v>
+      </c>
+      <c r="CO141" t="n">
+        <v>0.32804</v>
+      </c>
+      <c r="CP141" t="n">
+        <v>0.32668</v>
+      </c>
+      <c r="CQ141" t="n">
+        <v>0.29064</v>
+      </c>
+      <c r="CR141" t="n">
+        <v>0.28919</v>
+      </c>
+      <c r="CS141" t="n">
+        <v>0.3052</v>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" s="2" t="n">
+        <v>46165</v>
+      </c>
+      <c r="B142" t="n">
+        <v>0.34318</v>
+      </c>
+      <c r="C142" t="n">
+        <v>0.58469</v>
+      </c>
+      <c r="D142" t="n">
+        <v>0.34759</v>
+      </c>
+      <c r="E142" t="n">
+        <v>0.34202</v>
+      </c>
+      <c r="F142" t="n">
+        <v>0.36765</v>
+      </c>
+      <c r="G142" t="n">
+        <v>0.35099</v>
+      </c>
+      <c r="H142" t="n">
+        <v>0.32721</v>
+      </c>
+      <c r="I142" t="n">
+        <v>0.29864</v>
+      </c>
+      <c r="J142" t="n">
+        <v>0.33529</v>
+      </c>
+      <c r="K142" t="n">
+        <v>0.31332</v>
+      </c>
+      <c r="L142" t="n">
+        <v>0.32677</v>
+      </c>
+      <c r="M142" t="n">
+        <v>0.3298</v>
+      </c>
+      <c r="N142" t="n">
+        <v>0.33899</v>
+      </c>
+      <c r="O142" t="n">
+        <v>0.33086</v>
+      </c>
+      <c r="P142" t="n">
+        <v>0.32821</v>
+      </c>
+      <c r="Q142" t="n">
+        <v>0.31882</v>
+      </c>
+      <c r="R142" t="n">
+        <v>0.33018</v>
+      </c>
+      <c r="S142" t="n">
+        <v>0.33063</v>
+      </c>
+      <c r="T142" t="n">
+        <v>0.33137</v>
+      </c>
+      <c r="U142" t="n">
+        <v>0.32624</v>
+      </c>
+      <c r="V142" t="n">
+        <v>0.31913</v>
+      </c>
+      <c r="W142" t="n">
+        <v>0.32554</v>
+      </c>
+      <c r="X142" t="n">
+        <v>0.32519</v>
+      </c>
+      <c r="Y142" t="n">
+        <v>0.32872</v>
+      </c>
+      <c r="Z142" t="n">
+        <v>0.3215</v>
+      </c>
+      <c r="AA142" t="n">
+        <v>0.30849</v>
+      </c>
+      <c r="AB142" t="n">
+        <v>0.32465</v>
+      </c>
+      <c r="AC142" t="n">
+        <v>0.31794</v>
+      </c>
+      <c r="AD142" t="n">
+        <v>0.33201</v>
+      </c>
+      <c r="AE142" t="n">
+        <v>0.3298</v>
+      </c>
+      <c r="AF142" t="n">
+        <v>0.31891</v>
+      </c>
+      <c r="AG142" t="n">
+        <v>0.31371</v>
+      </c>
+      <c r="AH142" t="n">
+        <v>0.31688</v>
+      </c>
+      <c r="AI142" t="n">
+        <v>0.32258</v>
+      </c>
+      <c r="AJ142" t="n">
+        <v>0.3291</v>
+      </c>
+      <c r="AK142" t="n">
+        <v>0.32901</v>
+      </c>
+      <c r="AL142" t="n">
+        <v>0.33043</v>
+      </c>
+      <c r="AM142" t="n">
+        <v>0.33858</v>
+      </c>
+      <c r="AN142" t="n">
+        <v>0.31599</v>
+      </c>
+      <c r="AO142" t="n">
+        <v>0.31987</v>
+      </c>
+      <c r="AP142" t="n">
+        <v>0.34839</v>
+      </c>
+      <c r="AQ142" t="n">
+        <v>0.26789</v>
+      </c>
+      <c r="AR142" t="n">
+        <v>0.304</v>
+      </c>
+      <c r="AS142" t="n">
+        <v>0.28509</v>
+      </c>
+      <c r="AT142" t="n">
+        <v>0.31672</v>
+      </c>
+      <c r="AU142" t="n">
+        <v>0.15495</v>
+      </c>
+      <c r="AV142" t="n">
+        <v>0.3023</v>
+      </c>
+      <c r="AW142" t="n">
+        <v>0.29547</v>
+      </c>
+      <c r="AX142" t="n">
+        <v>0.28987</v>
+      </c>
+      <c r="AY142" t="n">
+        <v>0.35392</v>
+      </c>
+      <c r="AZ142" t="n">
+        <v>0.29346</v>
+      </c>
+      <c r="BA142" t="n">
+        <v>0.23846</v>
+      </c>
+      <c r="BB142" t="n">
+        <v>0.11789</v>
+      </c>
+      <c r="BC142" t="n">
+        <v>0.29443</v>
+      </c>
+      <c r="BD142" t="n">
+        <v>0.28078</v>
+      </c>
+      <c r="BE142" t="n">
+        <v>0.42722</v>
+      </c>
+      <c r="BF142" t="n">
+        <v>0.2783</v>
+      </c>
+      <c r="BG142" t="n">
+        <v>0.32584</v>
+      </c>
+      <c r="BH142" t="n">
+        <v>0.31297</v>
+      </c>
+      <c r="BI142" t="n">
+        <v>0.35272</v>
+      </c>
+      <c r="BJ142" t="n">
+        <v>0.32318</v>
+      </c>
+      <c r="BK142" t="n">
+        <v>0.35113</v>
+      </c>
+      <c r="BL142" t="n">
+        <v>0.33304</v>
+      </c>
+      <c r="BM142" t="n">
+        <v>0.31161</v>
+      </c>
+      <c r="BN142" t="n">
+        <v>0.33052</v>
+      </c>
+      <c r="BO142" t="n">
+        <v>0.33517</v>
+      </c>
+      <c r="BP142" t="n">
+        <v>0.32133</v>
+      </c>
+      <c r="BQ142" t="n">
+        <v>0.41402</v>
+      </c>
+      <c r="BR142" t="n">
+        <v>0.41962</v>
+      </c>
+      <c r="BS142" t="n">
+        <v>0.43702</v>
+      </c>
+      <c r="BT142" t="n">
+        <v>0.43014</v>
+      </c>
+      <c r="BU142" t="n">
+        <v>0.42924</v>
+      </c>
+      <c r="BV142" t="n">
+        <v>0.3482</v>
+      </c>
+      <c r="BW142" t="n">
+        <v>0.33523</v>
+      </c>
+      <c r="BX142" t="n">
+        <v>0.36581</v>
+      </c>
+      <c r="BY142" t="n">
+        <v>0.34326</v>
+      </c>
+      <c r="BZ142" t="n">
+        <v>0.32637</v>
+      </c>
+      <c r="CA142" t="n">
+        <v>0.36748</v>
+      </c>
+      <c r="CB142" t="n">
+        <v>0.36193</v>
+      </c>
+      <c r="CC142" t="n">
+        <v>0.32353</v>
+      </c>
+      <c r="CD142" t="n">
+        <v>0.34932</v>
+      </c>
+      <c r="CE142" t="n">
+        <v>0.35836</v>
+      </c>
+      <c r="CF142" t="n">
+        <v>0.34637</v>
+      </c>
+      <c r="CG142" t="n">
+        <v>0.35095</v>
+      </c>
+      <c r="CH142" t="n">
+        <v>0.34562</v>
+      </c>
+      <c r="CI142" t="n">
+        <v>0.40983</v>
+      </c>
+      <c r="CJ142" t="n">
+        <v>0.35038</v>
+      </c>
+      <c r="CK142" t="n">
+        <v>0.34417</v>
+      </c>
+      <c r="CL142" t="n">
+        <v>0.42343</v>
+      </c>
+      <c r="CM142" t="n">
+        <v>0.35855</v>
+      </c>
+      <c r="CN142" t="n">
+        <v>0.35511</v>
+      </c>
+      <c r="CO142" t="n">
+        <v>0.32166</v>
+      </c>
+      <c r="CP142" t="n">
+        <v>0.32324</v>
+      </c>
+      <c r="CQ142" t="n">
+        <v>0.32551</v>
+      </c>
+      <c r="CR142" t="n">
+        <v>0.32668</v>
+      </c>
+      <c r="CS142" t="n">
+        <v>0.32571</v>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" s="2" t="n">
+        <v>46166</v>
+      </c>
+      <c r="B143" t="n">
+        <v>0.34869</v>
+      </c>
+      <c r="C143" t="n">
+        <v>0.36389</v>
+      </c>
+      <c r="D143" t="n">
+        <v>0.35677</v>
+      </c>
+      <c r="E143" t="n">
+        <v>0.27117</v>
+      </c>
+      <c r="F143" t="n">
+        <v>0.37294</v>
+      </c>
+      <c r="G143" t="n">
+        <v>0.34784</v>
+      </c>
+      <c r="H143" t="n">
+        <v>0.34506</v>
+      </c>
+      <c r="I143" t="n">
+        <v>0.32677</v>
+      </c>
+      <c r="J143" t="n">
+        <v>0.32658</v>
+      </c>
+      <c r="K143" t="n">
+        <v>0.32592</v>
+      </c>
+      <c r="L143" t="n">
+        <v>0.32762</v>
+      </c>
+      <c r="M143" t="n">
+        <v>0.32262</v>
+      </c>
+      <c r="N143" t="n">
+        <v>0.32803</v>
+      </c>
+      <c r="O143" t="n">
+        <v>0.33838</v>
+      </c>
+      <c r="P143" t="n">
+        <v>0.29668</v>
+      </c>
+      <c r="Q143" t="n">
+        <v>0.35082</v>
+      </c>
+      <c r="R143" t="n">
+        <v>0.34176</v>
+      </c>
+      <c r="S143" t="n">
+        <v>0.32491</v>
+      </c>
+      <c r="T143" t="n">
+        <v>0.31068</v>
+      </c>
+      <c r="U143" t="n">
+        <v>0.31532</v>
+      </c>
+      <c r="V143" t="n">
+        <v>0.31473</v>
+      </c>
+      <c r="W143" t="n">
+        <v>0.31521</v>
+      </c>
+      <c r="X143" t="n">
+        <v>0.32347</v>
+      </c>
+      <c r="Y143" t="n">
+        <v>0.32</v>
+      </c>
+      <c r="Z143" t="n">
+        <v>0.32199</v>
+      </c>
+      <c r="AA143" t="n">
+        <v>0.31025</v>
+      </c>
+      <c r="AB143" t="n">
+        <v>0.32303</v>
+      </c>
+      <c r="AC143" t="n">
+        <v>0.31911</v>
+      </c>
+      <c r="AD143" t="n">
+        <v>0.31946</v>
+      </c>
+      <c r="AE143" t="n">
+        <v>0.31696</v>
+      </c>
+      <c r="AF143" t="n">
+        <v>0.30138</v>
+      </c>
+      <c r="AG143" t="n">
+        <v>0.32012</v>
+      </c>
+      <c r="AH143" t="n">
+        <v>0.30296</v>
+      </c>
+      <c r="AI143" t="n">
+        <v>0.17677</v>
+      </c>
+      <c r="AJ143" t="n">
+        <v>0.30264</v>
+      </c>
+      <c r="AK143" t="n">
+        <v>0.2891</v>
+      </c>
+      <c r="AL143" t="n">
+        <v>0.31315</v>
+      </c>
+      <c r="AM143" t="n">
+        <v>0.14641</v>
+      </c>
+      <c r="AN143" t="n">
+        <v>0.1996</v>
+      </c>
+      <c r="AO143" t="n">
+        <v>-0.0497</v>
+      </c>
+      <c r="AP143" t="n">
+        <v>0.23723</v>
+      </c>
+      <c r="AQ143" t="n">
+        <v>-0.04749</v>
+      </c>
+      <c r="AR143" t="n">
+        <v>-0.04767</v>
+      </c>
+      <c r="AS143" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AT143" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AU143" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AV143" t="n">
+        <v>0.13428</v>
+      </c>
+      <c r="AW143" t="n">
+        <v>-0.00044</v>
+      </c>
+      <c r="AX143" t="n">
+        <v>0.03521</v>
+      </c>
+      <c r="AY143" t="n">
+        <v>0.17759</v>
+      </c>
+      <c r="AZ143" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BA143" t="n">
+        <v>0.22781</v>
+      </c>
+      <c r="BB143" t="n">
+        <v>0.27088</v>
+      </c>
+      <c r="BC143" t="n">
+        <v>0.15793</v>
+      </c>
+      <c r="BD143" t="n">
+        <v>0.24181</v>
+      </c>
+      <c r="BE143" t="n">
+        <v>0.31033</v>
+      </c>
+      <c r="BF143" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BG143" t="n">
+        <v>0.22089</v>
+      </c>
+      <c r="BH143" t="n">
+        <v>-0.003</v>
+      </c>
+      <c r="BI143" t="n">
+        <v>0.20209</v>
+      </c>
+      <c r="BJ143" t="n">
+        <v>0.15156</v>
+      </c>
+      <c r="BK143" t="n">
+        <v>0.26439</v>
+      </c>
+      <c r="BL143" t="n">
+        <v>0.2765</v>
+      </c>
+      <c r="BM143" t="n">
+        <v>0.32409</v>
+      </c>
+      <c r="BN143" t="n">
+        <v>0.29122</v>
+      </c>
+      <c r="BO143" t="n">
+        <v>0.31834</v>
+      </c>
+      <c r="BP143" t="n">
+        <v>0.35112</v>
+      </c>
+      <c r="BQ143" t="n">
+        <v>0.3661</v>
+      </c>
+      <c r="BR143" t="n">
+        <v>0.37795</v>
+      </c>
+      <c r="BS143" t="n">
+        <v>0.47664</v>
+      </c>
+      <c r="BT143" t="n">
+        <v>0.3868</v>
+      </c>
+      <c r="BU143" t="n">
+        <v>0.39078</v>
+      </c>
+      <c r="BV143" t="n">
+        <v>0.35952</v>
+      </c>
+      <c r="BW143" t="n">
+        <v>0.39292</v>
+      </c>
+      <c r="BX143" t="n">
+        <v>0.40512</v>
+      </c>
+      <c r="BY143" t="n">
+        <v>0.38087</v>
+      </c>
+      <c r="BZ143" t="n">
+        <v>0.31596</v>
+      </c>
+      <c r="CA143" t="n">
+        <v>0.38829</v>
+      </c>
+      <c r="CB143" t="n">
+        <v>0.33619</v>
+      </c>
+      <c r="CC143" t="n">
+        <v>0.38888</v>
+      </c>
+      <c r="CD143" t="n">
+        <v>0.42837</v>
+      </c>
+      <c r="CE143" t="n">
+        <v>0.41643</v>
+      </c>
+      <c r="CF143" t="n">
+        <v>0.35476</v>
+      </c>
+      <c r="CG143" t="n">
+        <v>0.41102</v>
+      </c>
+      <c r="CH143" t="n">
+        <v>0.35159</v>
+      </c>
+      <c r="CI143" t="n">
+        <v>0.40126</v>
+      </c>
+      <c r="CJ143" t="n">
+        <v>0.41738</v>
+      </c>
+      <c r="CK143" t="n">
+        <v>0.44928</v>
+      </c>
+      <c r="CL143" t="n">
+        <v>1.40148</v>
+      </c>
+      <c r="CM143" t="n">
+        <v>1.37076</v>
+      </c>
+      <c r="CN143" t="n">
+        <v>0.3456</v>
+      </c>
+      <c r="CO143" t="n">
+        <v>0.36707</v>
+      </c>
+      <c r="CP143" t="n">
+        <v>1.37514</v>
+      </c>
+      <c r="CQ143" t="n">
+        <v>1.35377</v>
+      </c>
+      <c r="CR143" t="n">
+        <v>0.35587</v>
+      </c>
+      <c r="CS143" t="n">
+        <v>0.3598</v>
       </c>
     </row>
   </sheetData>
